--- a/Distribucion/Excels/UFD.xlsx
+++ b/Distribucion/Excels/UFD.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E348"/>
+  <dimension ref="A1:G348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,16 @@
           <t>Subestacion_REE</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Longitud</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Latitud</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -477,6 +487,12 @@
           <t>NARCEA 400</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>-6.395362400961021</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.29202155679044</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,6 +516,12 @@
           <t>VILLAVICIOSA 400</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v>-4.525019196592187</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40.42657333373005</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +545,12 @@
           <t>VILLAVICIOSA 400</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>-4.44165662812342</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40.4129319236209</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -546,6 +574,12 @@
           <t>ZAL 220</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>2.131264233372755</v>
+      </c>
+      <c r="G5" t="n">
+        <v>41.31292701121468</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -569,6 +603,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>-4.355794144138794</v>
+      </c>
+      <c r="G6" t="n">
+        <v>38.88969896433933</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -592,6 +632,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>-4.090315648307038</v>
+      </c>
+      <c r="G7" t="n">
+        <v>38.71438054108086</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,6 +661,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F8" t="n">
+        <v>-3.982490369939146</v>
+      </c>
+      <c r="G8" t="n">
+        <v>38.87663116446411</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -638,6 +690,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>-3.074458682835742</v>
+      </c>
+      <c r="G9" t="n">
+        <v>39.13761781669608</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -661,6 +719,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F10" t="n">
+        <v>-3.961734680718936</v>
+      </c>
+      <c r="G10" t="n">
+        <v>38.9480376638934</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,6 +748,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F11" t="n">
+        <v>-4.838600962461556</v>
+      </c>
+      <c r="G11" t="n">
+        <v>38.77036164981274</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -707,6 +777,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F12" t="n">
+        <v>-3.72085403952196</v>
+      </c>
+      <c r="G12" t="n">
+        <v>38.89102915427546</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -730,6 +806,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F13" t="n">
+        <v>-3.169679351078285</v>
+      </c>
+      <c r="G13" t="n">
+        <v>38.87332361509112</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -753,6 +835,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F14" t="n">
+        <v>-3.493306629995575</v>
+      </c>
+      <c r="G14" t="n">
+        <v>38.51918028644226</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -776,6 +864,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F15" t="n">
+        <v>-4.170981440896143</v>
+      </c>
+      <c r="G15" t="n">
+        <v>38.71740322779228</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -799,6 +893,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F16" t="n">
+        <v>-3.215193036867368</v>
+      </c>
+      <c r="G16" t="n">
+        <v>39.37950393532849</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -822,6 +922,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F17" t="n">
+        <v>-3.228673304768358</v>
+      </c>
+      <c r="G17" t="n">
+        <v>39.41159246557578</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -845,6 +951,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F18" t="n">
+        <v>-3.231916826806045</v>
+      </c>
+      <c r="G18" t="n">
+        <v>39.17687949177368</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -868,6 +980,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F19" t="n">
+        <v>-3.76939139614651</v>
+      </c>
+      <c r="G19" t="n">
+        <v>38.70301898497836</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -891,6 +1009,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>-3.919944979075234</v>
+      </c>
+      <c r="G20" t="n">
+        <v>38.97624609210852</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -914,6 +1038,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F21" t="n">
+        <v>-3.110079434721681</v>
+      </c>
+      <c r="G21" t="n">
+        <v>39.39313093648841</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -937,6 +1067,12 @@
           <t>LA SOLANA 220</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>-4.144143389765076</v>
+      </c>
+      <c r="G22" t="n">
+        <v>38.67895587215097</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -960,6 +1096,12 @@
           <t>LA SOLANA 220</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>-4.119271662289518</v>
+      </c>
+      <c r="G23" t="n">
+        <v>38.67934075028865</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -983,6 +1125,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F24" t="n">
+        <v>-3.158659978619218</v>
+      </c>
+      <c r="G24" t="n">
+        <v>38.85835288528049</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1006,6 +1154,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>-3.595186271623654</v>
+      </c>
+      <c r="G25" t="n">
+        <v>39.07081858539385</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1029,6 +1183,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F26" t="n">
+        <v>-3.621615977900038</v>
+      </c>
+      <c r="G26" t="n">
+        <v>39.07258204350319</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1052,6 +1212,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F27" t="n">
+        <v>-4.288425659901504</v>
+      </c>
+      <c r="G27" t="n">
+        <v>39.21849095180031</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1075,6 +1241,12 @@
           <t>LA SOLANA 220</t>
         </is>
       </c>
+      <c r="F28" t="n">
+        <v>-4.475000594850432</v>
+      </c>
+      <c r="G28" t="n">
+        <v>38.47196374915249</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1098,6 +1270,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F29" t="n">
+        <v>-3.318871864782004</v>
+      </c>
+      <c r="G29" t="n">
+        <v>39.11230766670364</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1121,6 +1299,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F30" t="n">
+        <v>-3.392079656028046</v>
+      </c>
+      <c r="G30" t="n">
+        <v>39.17109810009563</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1144,6 +1328,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F31" t="n">
+        <v>-3.864499993305085</v>
+      </c>
+      <c r="G31" t="n">
+        <v>39.16970433862709</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1167,6 +1357,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F32" t="n">
+        <v>-3.360931601883706</v>
+      </c>
+      <c r="G32" t="n">
+        <v>39.29623480110987</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1190,6 +1386,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F33" t="n">
+        <v>-3.552735969909441</v>
+      </c>
+      <c r="G33" t="n">
+        <v>38.8193584541234</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1213,6 +1415,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F34" t="n">
+        <v>-2.921406088555321</v>
+      </c>
+      <c r="G34" t="n">
+        <v>38.56562276982844</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1236,6 +1444,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F35" t="n">
+        <v>-3.931465533377136</v>
+      </c>
+      <c r="G35" t="n">
+        <v>39.00438654026506</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1259,6 +1473,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F36" t="n">
+        <v>-2.954541402252929</v>
+      </c>
+      <c r="G36" t="n">
+        <v>39.40143697712289</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1282,6 +1502,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F37" t="n">
+        <v>-4.182835167825891</v>
+      </c>
+      <c r="G37" t="n">
+        <v>39.03279089334351</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1305,6 +1531,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F38" t="n">
+        <v>-3.374577429306396</v>
+      </c>
+      <c r="G38" t="n">
+        <v>39.02050695225117</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1328,6 +1560,12 @@
           <t>ALARCOS 220</t>
         </is>
       </c>
+      <c r="F39" t="n">
+        <v>-4.237391106566784</v>
+      </c>
+      <c r="G39" t="n">
+        <v>39.42272532376067</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1351,6 +1589,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F40" t="n">
+        <v>-2.995435726795475</v>
+      </c>
+      <c r="G40" t="n">
+        <v>39.2202821227261</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1374,6 +1618,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F41" t="n">
+        <v>-3.461865295502517</v>
+      </c>
+      <c r="G41" t="n">
+        <v>38.64661113004796</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1397,6 +1647,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F42" t="n">
+        <v>-2.801594352803412</v>
+      </c>
+      <c r="G42" t="n">
+        <v>39.29800385983495</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1420,6 +1676,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F43" t="n">
+        <v>-3.245292335067891</v>
+      </c>
+      <c r="G43" t="n">
+        <v>38.93073666194528</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1443,6 +1705,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F44" t="n">
+        <v>-3.026118270556458</v>
+      </c>
+      <c r="G44" t="n">
+        <v>39.17641349470038</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1466,6 +1734,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F45" t="n">
+        <v>-3.012899527058473</v>
+      </c>
+      <c r="G45" t="n">
+        <v>38.7444173206971</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1489,6 +1763,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F46" t="n">
+        <v>-2.846328507147116</v>
+      </c>
+      <c r="G46" t="n">
+        <v>38.75207613512946</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1512,6 +1792,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F47" t="n">
+        <v>-3.395348629453463</v>
+      </c>
+      <c r="G47" t="n">
+        <v>38.75653710202317</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1535,6 +1821,12 @@
           <t>LA PALOMA 220</t>
         </is>
       </c>
+      <c r="F48" t="n">
+        <v>-3.598857585970681</v>
+      </c>
+      <c r="G48" t="n">
+        <v>39.20956978723552</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1558,6 +1850,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F49" t="n">
+        <v>-2.786201410937087</v>
+      </c>
+      <c r="G49" t="n">
+        <v>40.39947041357562</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1581,6 +1879,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F50" t="n">
+        <v>-1.674184386444553</v>
+      </c>
+      <c r="G50" t="n">
+        <v>40.07201181996189</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1604,6 +1908,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F51" t="n">
+        <v>-1.644283969887206</v>
+      </c>
+      <c r="G51" t="n">
+        <v>40.04168284272767</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1627,6 +1937,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F52" t="n">
+        <v>-2.138939181475374</v>
+      </c>
+      <c r="G52" t="n">
+        <v>40.07769631168953</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1650,6 +1966,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F53" t="n">
+        <v>-1.376410630447749</v>
+      </c>
+      <c r="G53" t="n">
+        <v>39.90464976598741</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1673,6 +1995,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F54" t="n">
+        <v>-2.480125817532018</v>
+      </c>
+      <c r="G54" t="n">
+        <v>40.31319141271813</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1696,6 +2024,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F55" t="n">
+        <v>-2.074300544749366</v>
+      </c>
+      <c r="G55" t="n">
+        <v>40.23798778404076</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1719,6 +2053,12 @@
           <t>FUENTES DE LA ALCARRIA 400</t>
         </is>
       </c>
+      <c r="F56" t="n">
+        <v>-3.122997566310149</v>
+      </c>
+      <c r="G56" t="n">
+        <v>40.59076517850762</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1742,6 +2082,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F57" t="n">
+        <v>-2.967763093728638</v>
+      </c>
+      <c r="G57" t="n">
+        <v>40.26663250240857</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1765,6 +2111,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F58" t="n">
+        <v>-2.829325549426945</v>
+      </c>
+      <c r="G58" t="n">
+        <v>40.36433415203238</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1788,6 +2140,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F59" t="n">
+        <v>-2.876518316885032</v>
+      </c>
+      <c r="G59" t="n">
+        <v>40.72527463187998</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1811,6 +2169,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F60" t="n">
+        <v>-2.885778705765389</v>
+      </c>
+      <c r="G60" t="n">
+        <v>40.34954744157752</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1834,6 +2198,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F61" t="n">
+        <v>-3.200140857029728</v>
+      </c>
+      <c r="G61" t="n">
+        <v>40.57425209871404</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1857,6 +2227,12 @@
           <t>FUENTES DE LA ALCARRIA 400</t>
         </is>
       </c>
+      <c r="F62" t="n">
+        <v>-2.629061472023926</v>
+      </c>
+      <c r="G62" t="n">
+        <v>40.78645354249291</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1880,6 +2256,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F63" t="n">
+        <v>-2.750302881653869</v>
+      </c>
+      <c r="G63" t="n">
+        <v>40.49302996483427</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1903,6 +2285,12 @@
           <t>FUENTES DE LA ALCARRIA 400</t>
         </is>
       </c>
+      <c r="F64" t="n">
+        <v>-3.160502041942206</v>
+      </c>
+      <c r="G64" t="n">
+        <v>40.6185024582289</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1926,6 +2314,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F65" t="n">
+        <v>-3.091349302093465</v>
+      </c>
+      <c r="G65" t="n">
+        <v>40.37262240513472</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1949,6 +2343,12 @@
           <t>FUENTES DE LA ALCARRIA 400</t>
         </is>
       </c>
+      <c r="F66" t="n">
+        <v>-3.177385400061099</v>
+      </c>
+      <c r="G66" t="n">
+        <v>40.63670259631445</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1972,6 +2372,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F67" t="n">
+        <v>-2.833604530497016</v>
+      </c>
+      <c r="G67" t="n">
+        <v>40.2477778186573</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1995,6 +2401,12 @@
           <t>FUENTES DE LA ALCARRIA 400</t>
         </is>
       </c>
+      <c r="F68" t="n">
+        <v>-2.216204041220299</v>
+      </c>
+      <c r="G68" t="n">
+        <v>41.04687919995176</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2018,6 +2430,12 @@
           <t>FUENTES DE LA ALCARRIA 400</t>
         </is>
       </c>
+      <c r="F69" t="n">
+        <v>-1.882884556827424</v>
+      </c>
+      <c r="G69" t="n">
+        <v>40.83775483255648</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2041,6 +2459,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F70" t="n">
+        <v>-2.752058789941662</v>
+      </c>
+      <c r="G70" t="n">
+        <v>40.58975376907742</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2064,6 +2488,12 @@
           <t>BOLARQUE 220</t>
         </is>
       </c>
+      <c r="F71" t="n">
+        <v>-2.898959247376492</v>
+      </c>
+      <c r="G71" t="n">
+        <v>40.33905490569617</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2087,6 +2517,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F72" t="n">
+        <v>-2.174211171467115</v>
+      </c>
+      <c r="G72" t="n">
+        <v>43.47500810572026</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2110,6 +2546,12 @@
           <t>SABÓN 220</t>
         </is>
       </c>
+      <c r="F73" t="n">
+        <v>-2.240192144041855</v>
+      </c>
+      <c r="G73" t="n">
+        <v>43.27984396768383</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2133,6 +2575,12 @@
           <t>VIMIANZO 220</t>
         </is>
       </c>
+      <c r="F74" t="n">
+        <v>-2.774502628858523</v>
+      </c>
+      <c r="G74" t="n">
+        <v>43.09694375977974</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2156,6 +2604,12 @@
           <t>TAMBRE II 220</t>
         </is>
       </c>
+      <c r="F75" t="n">
+        <v>-2.871045447463434</v>
+      </c>
+      <c r="G75" t="n">
+        <v>42.66969401566848</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2179,6 +2633,12 @@
           <t>SABÓN 220</t>
         </is>
       </c>
+      <c r="F76" t="n">
+        <v>-2.68160272353976</v>
+      </c>
+      <c r="G76" t="n">
+        <v>43.23245265940853</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2202,6 +2662,12 @@
           <t>VIMIANZO 220</t>
         </is>
       </c>
+      <c r="F77" t="n">
+        <v>-2.886104025481511</v>
+      </c>
+      <c r="G77" t="n">
+        <v>43.2152617988873</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2225,6 +2691,12 @@
           <t>SABÓN 220</t>
         </is>
       </c>
+      <c r="F78" t="n">
+        <v>-2.68508100479393</v>
+      </c>
+      <c r="G78" t="n">
+        <v>43.20508788880588</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2248,6 +2720,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F79" t="n">
+        <v>-2.037875006717189</v>
+      </c>
+      <c r="G79" t="n">
+        <v>43.63811475406554</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2271,6 +2749,12 @@
           <t>MESON DO VENTO 220</t>
         </is>
       </c>
+      <c r="F80" t="n">
+        <v>-2.155678559161327</v>
+      </c>
+      <c r="G80" t="n">
+        <v>43.13639179065881</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2294,6 +2778,12 @@
           <t>TAMBRE II 220</t>
         </is>
       </c>
+      <c r="F81" t="n">
+        <v>-2.792472124349327</v>
+      </c>
+      <c r="G81" t="n">
+        <v>43.02645068447703</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2317,6 +2807,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F82" t="n">
+        <v>-2.169491784807053</v>
+      </c>
+      <c r="G82" t="n">
+        <v>43.50902804182268</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2340,6 +2836,12 @@
           <t>VIMIANZO 220</t>
         </is>
       </c>
+      <c r="F83" t="n">
+        <v>-2.925131125855081</v>
+      </c>
+      <c r="G83" t="n">
+        <v>43.16584869872062</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2363,6 +2865,12 @@
           <t>VIMIANZO 220</t>
         </is>
       </c>
+      <c r="F84" t="n">
+        <v>-3.173316750723833</v>
+      </c>
+      <c r="G84" t="n">
+        <v>43.15588163178695</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2386,6 +2894,12 @@
           <t>EIRIS 220</t>
         </is>
       </c>
+      <c r="F85" t="n">
+        <v>-2.397867553555295</v>
+      </c>
+      <c r="G85" t="n">
+        <v>43.3429952237728</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2409,6 +2923,12 @@
           <t>PUERTO 220</t>
         </is>
       </c>
+      <c r="F86" t="n">
+        <v>-2.402150321917203</v>
+      </c>
+      <c r="G86" t="n">
+        <v>43.3667085330877</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2432,6 +2952,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F87" t="n">
+        <v>-2.044216515493278</v>
+      </c>
+      <c r="G87" t="n">
+        <v>43.40572455733638</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2455,6 +2981,12 @@
           <t>SANTIAGO DE COMPOSTELA 220</t>
         </is>
       </c>
+      <c r="F88" t="n">
+        <v>-2.494580881167854</v>
+      </c>
+      <c r="G88" t="n">
+        <v>42.91448981657607</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2478,6 +3010,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F89" t="n">
+        <v>-2.039251087391115</v>
+      </c>
+      <c r="G89" t="n">
+        <v>43.47448498763491</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2501,6 +3039,12 @@
           <t>GRELA 220</t>
         </is>
       </c>
+      <c r="F90" t="n">
+        <v>-2.42914606085572</v>
+      </c>
+      <c r="G90" t="n">
+        <v>43.34267837884101</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2524,6 +3068,12 @@
           <t>SABÓN 220</t>
         </is>
       </c>
+      <c r="F91" t="n">
+        <v>-2.579298052207804</v>
+      </c>
+      <c r="G91" t="n">
+        <v>43.25069886284857</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2547,6 +3097,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F92" t="n">
+        <v>-1.891476985680837</v>
+      </c>
+      <c r="G92" t="n">
+        <v>43.66476411329241</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2570,6 +3126,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F93" t="n">
+        <v>-2.163011794701776</v>
+      </c>
+      <c r="G93" t="n">
+        <v>43.51332082760207</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2593,6 +3155,12 @@
           <t>MEIRAMA 220</t>
         </is>
       </c>
+      <c r="F94" t="n">
+        <v>-2.409555530265396</v>
+      </c>
+      <c r="G94" t="n">
+        <v>43.16913122769822</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2616,6 +3184,12 @@
           <t>PORTODEMOUROS 220</t>
         </is>
       </c>
+      <c r="F95" t="n">
+        <v>-2.034987142553175</v>
+      </c>
+      <c r="G95" t="n">
+        <v>42.91203337016726</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2639,6 +3213,12 @@
           <t>MESON DO VENTO 220</t>
         </is>
       </c>
+      <c r="F96" t="n">
+        <v>-2.355891201124099</v>
+      </c>
+      <c r="G96" t="n">
+        <v>43.16806728416135</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2662,6 +3242,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F97" t="n">
+        <v>-1.854174842692247</v>
+      </c>
+      <c r="G97" t="n">
+        <v>43.43377350401617</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2685,6 +3271,12 @@
           <t>SABÓN 220</t>
         </is>
       </c>
+      <c r="F98" t="n">
+        <v>-2.487139675594317</v>
+      </c>
+      <c r="G98" t="n">
+        <v>43.29924499084158</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2708,6 +3300,12 @@
           <t>TAMBRE II 220</t>
         </is>
       </c>
+      <c r="F99" t="n">
+        <v>-3.074212650517391</v>
+      </c>
+      <c r="G99" t="n">
+        <v>42.78498620464142</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2731,6 +3329,12 @@
           <t>VIMIANZO 220</t>
         </is>
       </c>
+      <c r="F100" t="n">
+        <v>-3.233269457741351</v>
+      </c>
+      <c r="G100" t="n">
+        <v>43.05644186060967</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2754,6 +3358,12 @@
           <t>MAZARICOS 220</t>
         </is>
       </c>
+      <c r="F101" t="n">
+        <v>-3.029772958994332</v>
+      </c>
+      <c r="G101" t="n">
+        <v>42.89176475443433</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2777,6 +3387,12 @@
           <t>TAMBRE II 220</t>
         </is>
       </c>
+      <c r="F102" t="n">
+        <v>-2.73581077192851</v>
+      </c>
+      <c r="G102" t="n">
+        <v>42.91584098081738</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2800,6 +3416,12 @@
           <t>TAMBRE II 220</t>
         </is>
       </c>
+      <c r="F103" t="n">
+        <v>-2.657381628969842</v>
+      </c>
+      <c r="G103" t="n">
+        <v>42.74162276938289</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2823,6 +3445,12 @@
           <t>TAMBRE II 220</t>
         </is>
       </c>
+      <c r="F104" t="n">
+        <v>-2.985867677575239</v>
+      </c>
+      <c r="G104" t="n">
+        <v>42.72640173899076</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2846,6 +3474,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F105" t="n">
+        <v>-2.211212977030921</v>
+      </c>
+      <c r="G105" t="n">
+        <v>43.32495874830874</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2869,6 +3503,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F106" t="n">
+        <v>-2.320901966195391</v>
+      </c>
+      <c r="G106" t="n">
+        <v>43.46831076142712</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2892,6 +3532,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F107" t="n">
+        <v>-1.860044584584739</v>
+      </c>
+      <c r="G107" t="n">
+        <v>43.43965795680131</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2915,6 +3561,12 @@
           <t>TAMBRE II 220</t>
         </is>
       </c>
+      <c r="F108" t="n">
+        <v>-2.970779891400893</v>
+      </c>
+      <c r="G108" t="n">
+        <v>42.57583356681521</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2938,6 +3590,12 @@
           <t>VIMIANZO 220</t>
         </is>
       </c>
+      <c r="F109" t="n">
+        <v>-3.170155862037196</v>
+      </c>
+      <c r="G109" t="n">
+        <v>42.94717734094524</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2961,6 +3619,12 @@
           <t>SABÓN 220</t>
         </is>
       </c>
+      <c r="F110" t="n">
+        <v>-2.363095484119638</v>
+      </c>
+      <c r="G110" t="n">
+        <v>43.22533276302141</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2984,6 +3648,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F111" t="n">
+        <v>-2.207874117552794</v>
+      </c>
+      <c r="G111" t="n">
+        <v>43.54066208582352</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3007,6 +3677,12 @@
           <t>TAMBRE II 220</t>
         </is>
       </c>
+      <c r="F112" t="n">
+        <v>-2.737909566831735</v>
+      </c>
+      <c r="G112" t="n">
+        <v>42.78760107797914</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3030,6 +3706,12 @@
           <t>SABÓN 220</t>
         </is>
       </c>
+      <c r="F113" t="n">
+        <v>-2.308208095349812</v>
+      </c>
+      <c r="G113" t="n">
+        <v>43.3508622357155</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3053,6 +3735,12 @@
           <t>SABÓN 220</t>
         </is>
       </c>
+      <c r="F114" t="n">
+        <v>-2.500746070610181</v>
+      </c>
+      <c r="G114" t="n">
+        <v>43.32840797233777</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3076,6 +3764,12 @@
           <t>SAN CAYETANO 220</t>
         </is>
       </c>
+      <c r="F115" t="n">
+        <v>-2.531852548056411</v>
+      </c>
+      <c r="G115" t="n">
+        <v>42.89154990928035</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3099,6 +3793,12 @@
           <t>MESON DO VENTO 220</t>
         </is>
       </c>
+      <c r="F116" t="n">
+        <v>-2.023788849789965</v>
+      </c>
+      <c r="G116" t="n">
+        <v>43.15137999933746</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3122,6 +3822,12 @@
           <t>MESON DO VENTO 220</t>
         </is>
       </c>
+      <c r="F117" t="n">
+        <v>-2.444996988511889</v>
+      </c>
+      <c r="G117" t="n">
+        <v>42.98150156229158</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3145,6 +3851,12 @@
           <t>SABÓN 220</t>
         </is>
       </c>
+      <c r="F118" t="n">
+        <v>-2.348295207878113</v>
+      </c>
+      <c r="G118" t="n">
+        <v>43.30956877881584</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3168,6 +3880,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F119" t="n">
+        <v>-2.226178198668359</v>
+      </c>
+      <c r="G119" t="n">
+        <v>43.49438864972537</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3191,6 +3909,12 @@
           <t>SANTIAGO DE COMPOSTELA 220</t>
         </is>
       </c>
+      <c r="F120" t="n">
+        <v>-2.578347989771348</v>
+      </c>
+      <c r="G120" t="n">
+        <v>42.85479997194844</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3214,6 +3938,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F121" t="n">
+        <v>-1.922733702777709</v>
+      </c>
+      <c r="G121" t="n">
+        <v>43.53834885451514</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3237,6 +3967,12 @@
           <t>SABÓN 220</t>
         </is>
       </c>
+      <c r="F122" t="n">
+        <v>-2.435138506387183</v>
+      </c>
+      <c r="G122" t="n">
+        <v>43.36966761030885</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3260,6 +3996,12 @@
           <t>TAMBRE II 220</t>
         </is>
       </c>
+      <c r="F123" t="n">
+        <v>-2.845379957598933</v>
+      </c>
+      <c r="G123" t="n">
+        <v>42.8325263722349</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3283,6 +4025,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F124" t="n">
+        <v>-2.165856916196512</v>
+      </c>
+      <c r="G124" t="n">
+        <v>43.43965054963625</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3306,6 +4054,12 @@
           <t>VIMIANZO 220</t>
         </is>
       </c>
+      <c r="F125" t="n">
+        <v>-3.0483566689213</v>
+      </c>
+      <c r="G125" t="n">
+        <v>43.1011629158779</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3329,6 +4083,12 @@
           <t>SANTA MARINA 220</t>
         </is>
       </c>
+      <c r="F126" t="n">
+        <v>-6.383357472992295</v>
+      </c>
+      <c r="G126" t="n">
+        <v>42.59723915765961</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3352,6 +4112,12 @@
           <t>COMPOSTILLA 400</t>
         </is>
       </c>
+      <c r="F127" t="n">
+        <v>-6.615240235564064</v>
+      </c>
+      <c r="G127" t="n">
+        <v>42.76171315084262</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3375,6 +4141,12 @@
           <t>COMPOSTILLA 400</t>
         </is>
       </c>
+      <c r="F128" t="n">
+        <v>-6.054967042625179</v>
+      </c>
+      <c r="G128" t="n">
+        <v>42.4641201119811</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3398,6 +4170,12 @@
           <t>COMPOSTILLA 400</t>
         </is>
       </c>
+      <c r="F129" t="n">
+        <v>-5.889022966019015</v>
+      </c>
+      <c r="G129" t="n">
+        <v>42.29484626737356</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3421,6 +4199,12 @@
           <t>LA ROBLA 400</t>
         </is>
       </c>
+      <c r="F130" t="n">
+        <v>-5.803298004594409</v>
+      </c>
+      <c r="G130" t="n">
+        <v>42.61184367756623</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3444,6 +4228,12 @@
           <t>COMPOSTILLA 400</t>
         </is>
       </c>
+      <c r="F131" t="n">
+        <v>-6.653919027631547</v>
+      </c>
+      <c r="G131" t="n">
+        <v>42.56432939536405</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3467,6 +4257,12 @@
           <t>TRIVES 400</t>
         </is>
       </c>
+      <c r="F132" t="n">
+        <v>-6.756061835234611</v>
+      </c>
+      <c r="G132" t="n">
+        <v>42.48997941918184</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3490,6 +4286,12 @@
           <t>COMPOSTILLA 400</t>
         </is>
       </c>
+      <c r="F133" t="n">
+        <v>-6.771034408121371</v>
+      </c>
+      <c r="G133" t="n">
+        <v>42.57559356519173</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3513,6 +4315,12 @@
           <t>COMPOSTILLA 400</t>
         </is>
       </c>
+      <c r="F134" t="n">
+        <v>-6.60107238942097</v>
+      </c>
+      <c r="G134" t="n">
+        <v>42.61749976169468</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3536,6 +4344,12 @@
           <t>TRIVES 400</t>
         </is>
       </c>
+      <c r="F135" t="n">
+        <v>-6.56251785325269</v>
+      </c>
+      <c r="G135" t="n">
+        <v>42.27796238783072</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3559,6 +4373,12 @@
           <t>LA ROBLA 400</t>
         </is>
       </c>
+      <c r="F136" t="n">
+        <v>-5.816014761035306</v>
+      </c>
+      <c r="G136" t="n">
+        <v>42.69374479172913</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3582,6 +4402,12 @@
           <t>COMPOSTILLA 400</t>
         </is>
       </c>
+      <c r="F137" t="n">
+        <v>-6.633052811382157</v>
+      </c>
+      <c r="G137" t="n">
+        <v>42.75977110250703</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3605,6 +4431,12 @@
           <t>LA ROBLA 400</t>
         </is>
       </c>
+      <c r="F138" t="n">
+        <v>-5.89330266763617</v>
+      </c>
+      <c r="G138" t="n">
+        <v>42.45711660513202</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3628,6 +4460,12 @@
           <t>LA ROBLA 400</t>
         </is>
       </c>
+      <c r="F139" t="n">
+        <v>-5.661741009303019</v>
+      </c>
+      <c r="G139" t="n">
+        <v>42.24706670720717</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3651,6 +4489,12 @@
           <t>SANTA MARINA 220</t>
         </is>
       </c>
+      <c r="F140" t="n">
+        <v>-6.552909686864184</v>
+      </c>
+      <c r="G140" t="n">
+        <v>42.56895072482293</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3674,6 +4518,12 @@
           <t>COMPOSTILLA 400</t>
         </is>
       </c>
+      <c r="F141" t="n">
+        <v>-6.536038402962175</v>
+      </c>
+      <c r="G141" t="n">
+        <v>42.75387945677458</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3697,6 +4547,12 @@
           <t>COMPOSTILLA 400</t>
         </is>
       </c>
+      <c r="F142" t="n">
+        <v>-6.604951665031956</v>
+      </c>
+      <c r="G142" t="n">
+        <v>42.56073204066423</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3720,6 +4576,12 @@
           <t>SANTA MARINA 220</t>
         </is>
       </c>
+      <c r="F143" t="n">
+        <v>-6.46516768730042</v>
+      </c>
+      <c r="G143" t="n">
+        <v>42.62021944495033</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3743,6 +4605,12 @@
           <t>LA ROBLA 400</t>
         </is>
       </c>
+      <c r="F144" t="n">
+        <v>-5.634419667089037</v>
+      </c>
+      <c r="G144" t="n">
+        <v>42.79460818413451</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3766,6 +4634,12 @@
           <t>LA ROBLA 400</t>
         </is>
       </c>
+      <c r="F145" t="n">
+        <v>-5.83904837496772</v>
+      </c>
+      <c r="G145" t="n">
+        <v>42.82263479330186</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3789,6 +4663,12 @@
           <t>TRIVES 400</t>
         </is>
       </c>
+      <c r="F146" t="n">
+        <v>-6.670718530524439</v>
+      </c>
+      <c r="G146" t="n">
+        <v>42.41579772047478</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3812,6 +4692,12 @@
           <t>LA ROBLA 400</t>
         </is>
       </c>
+      <c r="F147" t="n">
+        <v>-5.742689814287713</v>
+      </c>
+      <c r="G147" t="n">
+        <v>42.35758821429417</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3835,6 +4721,12 @@
           <t>VILLABLINO 220</t>
         </is>
       </c>
+      <c r="F148" t="n">
+        <v>-6.287626470132684</v>
+      </c>
+      <c r="G148" t="n">
+        <v>42.93940065389307</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3858,6 +4750,12 @@
           <t>TRIVES 400</t>
         </is>
       </c>
+      <c r="F149" t="n">
+        <v>-6.805324099178047</v>
+      </c>
+      <c r="G149" t="n">
+        <v>42.59971464830666</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3881,6 +4779,12 @@
           <t>LA ROBLA 400</t>
         </is>
       </c>
+      <c r="F150" t="n">
+        <v>-5.755439884263684</v>
+      </c>
+      <c r="G150" t="n">
+        <v>42.53144846322846</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3904,6 +4808,12 @@
           <t>COMPOSTILLA 400</t>
         </is>
       </c>
+      <c r="F151" t="n">
+        <v>-6.761348720606572</v>
+      </c>
+      <c r="G151" t="n">
+        <v>42.5630365058289</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3927,6 +4837,12 @@
           <t>BELESAR 220</t>
         </is>
       </c>
+      <c r="F152" t="n">
+        <v>-1.713381094336294</v>
+      </c>
+      <c r="G152" t="n">
+        <v>42.62643782236754</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3950,6 +4866,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F153" t="n">
+        <v>-1.768447803816246</v>
+      </c>
+      <c r="G153" t="n">
+        <v>42.6254581272887</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3973,6 +4895,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F154" t="n">
+        <v>-1.359797716940234</v>
+      </c>
+      <c r="G154" t="n">
+        <v>42.92547519239591</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3996,6 +4924,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F155" t="n">
+        <v>-1.644123379212722</v>
+      </c>
+      <c r="G155" t="n">
+        <v>43.12370188347003</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4019,6 +4953,12 @@
           <t>PORTODEMOUROS 220</t>
         </is>
       </c>
+      <c r="F156" t="n">
+        <v>-1.8170406629779</v>
+      </c>
+      <c r="G156" t="n">
+        <v>43.02017378502241</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4042,6 +4982,12 @@
           <t>PUENTES GARCIA RODRIGUEZ 400</t>
         </is>
       </c>
+      <c r="F157" t="n">
+        <v>-1.573681207817912</v>
+      </c>
+      <c r="G157" t="n">
+        <v>43.01842584088055</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4065,6 +5011,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F158" t="n">
+        <v>-1.513478093681456</v>
+      </c>
+      <c r="G158" t="n">
+        <v>42.51128702634079</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4088,6 +5040,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F159" t="n">
+        <v>-1.247254582479423</v>
+      </c>
+      <c r="G159" t="n">
+        <v>42.79724179482108</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4111,6 +5069,12 @@
           <t>PORTODEMOUROS 220</t>
         </is>
       </c>
+      <c r="F160" t="n">
+        <v>-1.868485986668582</v>
+      </c>
+      <c r="G160" t="n">
+        <v>42.86631143036445</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4134,6 +5098,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F161" t="n">
+        <v>-1.726928488720461</v>
+      </c>
+      <c r="G161" t="n">
+        <v>42.46767617154996</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4157,6 +5127,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F162" t="n">
+        <v>-1.423614127886524</v>
+      </c>
+      <c r="G162" t="n">
+        <v>42.77632059449685</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4180,6 +5156,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F163" t="n">
+        <v>-1.227927718559496</v>
+      </c>
+      <c r="G163" t="n">
+        <v>42.75889770989652</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4203,6 +5185,12 @@
           <t>AENA 220</t>
         </is>
       </c>
+      <c r="F164" t="n">
+        <v>-3.597848976112254</v>
+      </c>
+      <c r="G164" t="n">
+        <v>40.50956406030083</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4226,6 +5214,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F165" t="n">
+        <v>-3.385985827993522</v>
+      </c>
+      <c r="G165" t="n">
+        <v>40.47756505524588</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4249,6 +5243,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F166" t="n">
+        <v>-3.319664254022979</v>
+      </c>
+      <c r="G166" t="n">
+        <v>40.51095669583575</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4272,6 +5272,12 @@
           <t>PUENTE SAN FERNANDO 220</t>
         </is>
       </c>
+      <c r="F167" t="n">
+        <v>-3.555111705356376</v>
+      </c>
+      <c r="G167" t="n">
+        <v>40.4453810005067</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4295,6 +5301,12 @@
           <t>ARGANDA 220</t>
         </is>
       </c>
+      <c r="F168" t="n">
+        <v>-3.459337731742458</v>
+      </c>
+      <c r="G168" t="n">
+        <v>40.30151933435215</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4318,6 +5330,12 @@
           <t>GETAFE 220</t>
         </is>
       </c>
+      <c r="F169" t="n">
+        <v>-3.678451683353023</v>
+      </c>
+      <c r="G169" t="n">
+        <v>40.27108073806115</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4341,6 +5359,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F170" t="n">
+        <v>-3.635551580456188</v>
+      </c>
+      <c r="G170" t="n">
+        <v>40.02487007308213</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4364,6 +5388,12 @@
           <t>AZCA 220</t>
         </is>
       </c>
+      <c r="F171" t="n">
+        <v>-3.694309357352976</v>
+      </c>
+      <c r="G171" t="n">
+        <v>40.45274586929609</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4387,6 +5417,12 @@
           <t>CANILLEJAS 220</t>
         </is>
       </c>
+      <c r="F172" t="n">
+        <v>-3.647042722546493</v>
+      </c>
+      <c r="G172" t="n">
+        <v>40.42822728009357</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4410,6 +5446,12 @@
           <t>COSLADA 220</t>
         </is>
       </c>
+      <c r="F173" t="n">
+        <v>-3.540926897934787</v>
+      </c>
+      <c r="G173" t="n">
+        <v>40.41313271861819</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4433,6 +5475,12 @@
           <t>GETAFE 220</t>
         </is>
       </c>
+      <c r="F174" t="n">
+        <v>-3.678055932863808</v>
+      </c>
+      <c r="G174" t="n">
+        <v>40.37619332238332</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4456,6 +5504,12 @@
           <t>GETAFE 220</t>
         </is>
       </c>
+      <c r="F175" t="n">
+        <v>-3.614693145841203</v>
+      </c>
+      <c r="G175" t="n">
+        <v>40.36337611788599</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4479,6 +5533,12 @@
           <t>CANILLEJAS 220</t>
         </is>
       </c>
+      <c r="F176" t="n">
+        <v>-3.658679783410706</v>
+      </c>
+      <c r="G176" t="n">
+        <v>40.43319761471844</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4502,6 +5562,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F177" t="n">
+        <v>-3.38091141908839</v>
+      </c>
+      <c r="G177" t="n">
+        <v>40.11061463926556</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4525,6 +5591,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F178" t="n">
+        <v>-3.574456316685664</v>
+      </c>
+      <c r="G178" t="n">
+        <v>40.03153186531861</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4548,6 +5620,12 @@
           <t>NORTE 220</t>
         </is>
       </c>
+      <c r="F179" t="n">
+        <v>-3.699839824946923</v>
+      </c>
+      <c r="G179" t="n">
+        <v>40.4549647650618</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4571,6 +5649,12 @@
           <t>COSLADA 220</t>
         </is>
       </c>
+      <c r="F180" t="n">
+        <v>-3.555122639011814</v>
+      </c>
+      <c r="G180" t="n">
+        <v>40.43954308739287</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4594,6 +5678,12 @@
           <t>CANILLEJAS 220</t>
         </is>
       </c>
+      <c r="F181" t="n">
+        <v>-3.614328099042631</v>
+      </c>
+      <c r="G181" t="n">
+        <v>40.43468505238382</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4617,6 +5707,12 @@
           <t>CERRO PLATA 220</t>
         </is>
       </c>
+      <c r="F182" t="n">
+        <v>-3.676647607702704</v>
+      </c>
+      <c r="G182" t="n">
+        <v>40.39673330446531</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4640,6 +5736,12 @@
           <t>COSLADA 220</t>
         </is>
       </c>
+      <c r="F183" t="n">
+        <v>-3.574833529058357</v>
+      </c>
+      <c r="G183" t="n">
+        <v>40.42250072032943</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4663,6 +5765,12 @@
           <t>COTO 220</t>
         </is>
       </c>
+      <c r="F184" t="n">
+        <v>-3.64344384433368</v>
+      </c>
+      <c r="G184" t="n">
+        <v>40.45014830804526</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4686,6 +5794,12 @@
           <t>CAMPO DE LAS NACIONES 220</t>
         </is>
       </c>
+      <c r="F185" t="n">
+        <v>-3.621334821399889</v>
+      </c>
+      <c r="G185" t="n">
+        <v>40.46450348554053</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4709,6 +5823,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F186" t="n">
+        <v>-3.53547789567</v>
+      </c>
+      <c r="G186" t="n">
+        <v>40.38738300720381</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4732,6 +5852,12 @@
           <t>VALLECAS 220</t>
         </is>
       </c>
+      <c r="F187" t="n">
+        <v>-3.627491677012812</v>
+      </c>
+      <c r="G187" t="n">
+        <v>40.399785309474</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4755,6 +5881,12 @@
           <t>PUENTE SAN FERNANDO 220</t>
         </is>
       </c>
+      <c r="F188" t="n">
+        <v>-3.534651611608661</v>
+      </c>
+      <c r="G188" t="n">
+        <v>40.44526122190692</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4778,6 +5910,12 @@
           <t>GETAFE 220</t>
         </is>
       </c>
+      <c r="F189" t="n">
+        <v>-3.691176627040166</v>
+      </c>
+      <c r="G189" t="n">
+        <v>40.31831291778062</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4801,6 +5939,12 @@
           <t>HORTALEZA 220</t>
         </is>
       </c>
+      <c r="F190" t="n">
+        <v>-3.664185744572088</v>
+      </c>
+      <c r="G190" t="n">
+        <v>40.4727336349738</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4824,6 +5968,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F191" t="n">
+        <v>-3.355483002714161</v>
+      </c>
+      <c r="G191" t="n">
+        <v>40.4317076528886</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4847,6 +5997,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F192" t="n">
+        <v>-3.467411245625164</v>
+      </c>
+      <c r="G192" t="n">
+        <v>40.4942644295235</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4870,6 +6026,12 @@
           <t>COSLADA 220</t>
         </is>
       </c>
+      <c r="F193" t="n">
+        <v>-3.58646398776193</v>
+      </c>
+      <c r="G193" t="n">
+        <v>40.4423613224911</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4893,6 +6055,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F194" t="n">
+        <v>-3.419840723032922</v>
+      </c>
+      <c r="G194" t="n">
+        <v>40.3877525528141</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4916,6 +6084,12 @@
           <t>VILLAVICIOSA 400</t>
         </is>
       </c>
+      <c r="F195" t="n">
+        <v>-4.247275439155096</v>
+      </c>
+      <c r="G195" t="n">
+        <v>40.3300947763623</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4939,6 +6113,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F196" t="n">
+        <v>-3.649857274239388</v>
+      </c>
+      <c r="G196" t="n">
+        <v>40.13183355340878</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4962,6 +6142,12 @@
           <t>MAZARREDO 220</t>
         </is>
       </c>
+      <c r="F197" t="n">
+        <v>-3.719083005020441</v>
+      </c>
+      <c r="G197" t="n">
+        <v>40.41253132996014</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4985,6 +6171,12 @@
           <t>MANUEL BECERRA 220</t>
         </is>
       </c>
+      <c r="F198" t="n">
+        <v>-3.660776787056754</v>
+      </c>
+      <c r="G198" t="n">
+        <v>40.43423970424779</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5008,6 +6200,12 @@
           <t>MEDIODIA 220</t>
         </is>
       </c>
+      <c r="F199" t="n">
+        <v>-3.691145946248243</v>
+      </c>
+      <c r="G199" t="n">
+        <v>40.40986385482613</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5031,6 +6229,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F200" t="n">
+        <v>-3.475707043856796</v>
+      </c>
+      <c r="G200" t="n">
+        <v>40.39055429147396</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5054,6 +6258,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F201" t="n">
+        <v>-3.656665995662451</v>
+      </c>
+      <c r="G201" t="n">
+        <v>40.36551481736337</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5077,6 +6287,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F202" t="n">
+        <v>-3.51300576459828</v>
+      </c>
+      <c r="G202" t="n">
+        <v>40.34024076566488</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5100,6 +6316,12 @@
           <t>VALLECAS 220</t>
         </is>
       </c>
+      <c r="F203" t="n">
+        <v>-3.641678515489344</v>
+      </c>
+      <c r="G203" t="n">
+        <v>40.40214891216787</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5123,6 +6345,12 @@
           <t>PUENTE SAN FERNANDO 220</t>
         </is>
       </c>
+      <c r="F204" t="n">
+        <v>-3.585937973012392</v>
+      </c>
+      <c r="G204" t="n">
+        <v>40.47547210504633</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5146,6 +6374,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F205" t="n">
+        <v>-3.240770367448169</v>
+      </c>
+      <c r="G205" t="n">
+        <v>40.37575927893204</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5169,6 +6403,12 @@
           <t>HORTALEZA 220</t>
         </is>
       </c>
+      <c r="F206" t="n">
+        <v>-3.693019582792567</v>
+      </c>
+      <c r="G206" t="n">
+        <v>40.44543830434013</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5192,6 +6432,12 @@
           <t>NORTE 220</t>
         </is>
       </c>
+      <c r="F207" t="n">
+        <v>-3.6993831020045</v>
+      </c>
+      <c r="G207" t="n">
+        <v>40.43024682225244</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5215,6 +6461,12 @@
           <t>VALLECAS 220</t>
         </is>
       </c>
+      <c r="F208" t="n">
+        <v>-3.655672480306101</v>
+      </c>
+      <c r="G208" t="n">
+        <v>40.41246687340204</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5238,6 +6490,12 @@
           <t>PUENTE PRINCESA 220</t>
         </is>
       </c>
+      <c r="F209" t="n">
+        <v>-3.706731246829301</v>
+      </c>
+      <c r="G209" t="n">
+        <v>40.4012831068146</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5261,6 +6519,12 @@
           <t>VALLECAS 220</t>
         </is>
       </c>
+      <c r="F210" t="n">
+        <v>-3.643598677008138</v>
+      </c>
+      <c r="G210" t="n">
+        <v>40.38846243610882</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5284,6 +6548,12 @@
           <t>CAMPO DE LAS NACIONES 220</t>
         </is>
       </c>
+      <c r="F211" t="n">
+        <v>-3.65618105560642</v>
+      </c>
+      <c r="G211" t="n">
+        <v>40.48176129305326</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5307,6 +6577,12 @@
           <t>ARGANDA 220</t>
         </is>
       </c>
+      <c r="F212" t="n">
+        <v>-3.481177734741631</v>
+      </c>
+      <c r="G212" t="n">
+        <v>40.32148518446506</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5330,6 +6606,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F213" t="n">
+        <v>-3.349831082157735</v>
+      </c>
+      <c r="G213" t="n">
+        <v>40.23474653842025</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5353,6 +6635,12 @@
           <t>PUENTE PRINCESA 220</t>
         </is>
       </c>
+      <c r="F214" t="n">
+        <v>-3.693248026771735</v>
+      </c>
+      <c r="G214" t="n">
+        <v>40.38385107563279</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5376,6 +6664,12 @@
           <t>PROSPERIDAD 220</t>
         </is>
       </c>
+      <c r="F215" t="n">
+        <v>-3.666578700788498</v>
+      </c>
+      <c r="G215" t="n">
+        <v>40.44271992042773</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5399,6 +6693,12 @@
           <t>CERRO PLATA 220</t>
         </is>
       </c>
+      <c r="F216" t="n">
+        <v>-3.690686584334083</v>
+      </c>
+      <c r="G216" t="n">
+        <v>40.42487566977773</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5422,6 +6722,12 @@
           <t>PUENTE SAN FERNANDO 220</t>
         </is>
       </c>
+      <c r="F217" t="n">
+        <v>-3.514201884330358</v>
+      </c>
+      <c r="G217" t="n">
+        <v>40.44958824440307</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5445,6 +6751,12 @@
           <t>GETAFE 220</t>
         </is>
       </c>
+      <c r="F218" t="n">
+        <v>-3.606279315464176</v>
+      </c>
+      <c r="G218" t="n">
+        <v>40.23122772807787</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5468,6 +6780,12 @@
           <t>COSLADA 220</t>
         </is>
       </c>
+      <c r="F219" t="n">
+        <v>-3.553208036082801</v>
+      </c>
+      <c r="G219" t="n">
+        <v>40.45338113929758</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5491,6 +6809,12 @@
           <t>PUENTE PRINCESA 220</t>
         </is>
       </c>
+      <c r="F220" t="n">
+        <v>-3.719212199175807</v>
+      </c>
+      <c r="G220" t="n">
+        <v>40.42355758599289</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5514,6 +6838,12 @@
           <t>COSLADA 220</t>
         </is>
       </c>
+      <c r="F221" t="n">
+        <v>-3.620884455597081</v>
+      </c>
+      <c r="G221" t="n">
+        <v>40.41556885000455</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5537,6 +6867,12 @@
           <t>CERRO PLATA 220</t>
         </is>
       </c>
+      <c r="F222" t="n">
+        <v>-3.681016509985653</v>
+      </c>
+      <c r="G222" t="n">
+        <v>40.42451862067425</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5560,6 +6896,12 @@
           <t>CERRO PLATA 220</t>
         </is>
       </c>
+      <c r="F223" t="n">
+        <v>-3.657448214115639</v>
+      </c>
+      <c r="G223" t="n">
+        <v>40.38419529039483</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5583,6 +6925,12 @@
           <t>NORTE 220</t>
         </is>
       </c>
+      <c r="F224" t="n">
+        <v>-3.688007296485774</v>
+      </c>
+      <c r="G224" t="n">
+        <v>40.42454930202416</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5606,6 +6954,12 @@
           <t>SIMANCAS 220</t>
         </is>
       </c>
+      <c r="F225" t="n">
+        <v>-3.630566584302784</v>
+      </c>
+      <c r="G225" t="n">
+        <v>40.43253455134089</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5629,6 +6983,12 @@
           <t>VILLAVICIOSA 400</t>
         </is>
       </c>
+      <c r="F226" t="n">
+        <v>-4.309324609711132</v>
+      </c>
+      <c r="G226" t="n">
+        <v>40.37217409551258</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5652,6 +7012,12 @@
           <t>GETAFE 220</t>
         </is>
       </c>
+      <c r="F227" t="n">
+        <v>-3.569246295326572</v>
+      </c>
+      <c r="G227" t="n">
+        <v>40.21372137076589</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5675,6 +7041,12 @@
           <t>GETAFE 220</t>
         </is>
       </c>
+      <c r="F228" t="n">
+        <v>-3.62788742814567</v>
+      </c>
+      <c r="G228" t="n">
+        <v>40.23535592312901</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5698,6 +7070,12 @@
           <t>VALLECAS 220</t>
         </is>
       </c>
+      <c r="F229" t="n">
+        <v>-3.619991191333272</v>
+      </c>
+      <c r="G229" t="n">
+        <v>40.3888707021576</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5721,6 +7099,12 @@
           <t>ARGANDA 220</t>
         </is>
       </c>
+      <c r="F230" t="n">
+        <v>-3.52601295350464</v>
+      </c>
+      <c r="G230" t="n">
+        <v>40.35049788136005</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5744,6 +7128,12 @@
           <t>VALLECAS 220</t>
         </is>
       </c>
+      <c r="F231" t="n">
+        <v>-3.581117377986083</v>
+      </c>
+      <c r="G231" t="n">
+        <v>40.33759425287283</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5767,6 +7157,12 @@
           <t>CAMPO DE LAS NACIONES 220</t>
         </is>
       </c>
+      <c r="F232" t="n">
+        <v>-3.603842453842396</v>
+      </c>
+      <c r="G232" t="n">
+        <v>40.48690242641074</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5790,6 +7186,12 @@
           <t>VALLECAS 220</t>
         </is>
       </c>
+      <c r="F233" t="n">
+        <v>-3.603226623953526</v>
+      </c>
+      <c r="G233" t="n">
+        <v>40.39695045089667</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5813,6 +7215,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F234" t="n">
+        <v>-3.644403543715642</v>
+      </c>
+      <c r="G234" t="n">
+        <v>40.16334313621518</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5836,6 +7244,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F235" t="n">
+        <v>-3.654675534313309</v>
+      </c>
+      <c r="G235" t="n">
+        <v>40.19356618739948</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5859,6 +7273,12 @@
           <t>VILLAVICIOSA 400</t>
         </is>
       </c>
+      <c r="F236" t="n">
+        <v>-3.904375297280548</v>
+      </c>
+      <c r="G236" t="n">
+        <v>40.34836543310954</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5882,6 +7302,12 @@
           <t>LOECHES 220</t>
         </is>
       </c>
+      <c r="F237" t="n">
+        <v>-3.291823401166353</v>
+      </c>
+      <c r="G237" t="n">
+        <v>40.17848108203169</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5905,6 +7331,12 @@
           <t>GETAFE 220</t>
         </is>
       </c>
+      <c r="F238" t="n">
+        <v>-3.690027080128177</v>
+      </c>
+      <c r="G238" t="n">
+        <v>40.36376200043104</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5928,6 +7360,12 @@
           <t>ALBARELLOS 220</t>
         </is>
       </c>
+      <c r="F239" t="n">
+        <v>-2.157289215320035</v>
+      </c>
+      <c r="G239" t="n">
+        <v>42.39795346412646</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5951,6 +7389,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F240" t="n">
+        <v>-1.794417155665992</v>
+      </c>
+      <c r="G240" t="n">
+        <v>42.18278182147874</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5974,6 +7418,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F241" t="n">
+        <v>-1.867053601225507</v>
+      </c>
+      <c r="G241" t="n">
+        <v>42.33619342330225</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5997,6 +7447,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F242" t="n">
+        <v>-1.005505072871706</v>
+      </c>
+      <c r="G242" t="n">
+        <v>42.4183605612434</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6020,6 +7476,12 @@
           <t>CASTRELO 220</t>
         </is>
       </c>
+      <c r="F243" t="n">
+        <v>-2.113717122508475</v>
+      </c>
+      <c r="G243" t="n">
+        <v>42.2916510045028</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -6043,6 +7505,12 @@
           <t>FRIEIRA 220</t>
         </is>
       </c>
+      <c r="F244" t="n">
+        <v>-2.055292777148656</v>
+      </c>
+      <c r="G244" t="n">
+        <v>41.94101731784708</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -6066,6 +7534,12 @@
           <t>FRIEIRA 220</t>
         </is>
       </c>
+      <c r="F245" t="n">
+        <v>-1.943185215918123</v>
+      </c>
+      <c r="G245" t="n">
+        <v>42.14602636633268</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -6089,6 +7563,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F246" t="n">
+        <v>-2.056415280275513</v>
+      </c>
+      <c r="G246" t="n">
+        <v>42.43603699374314</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -6112,6 +7592,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F247" t="n">
+        <v>-0.8625839321231518</v>
+      </c>
+      <c r="G247" t="n">
+        <v>42.38874939169047</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -6135,6 +7621,12 @@
           <t>FRIEIRA 220</t>
         </is>
       </c>
+      <c r="F248" t="n">
+        <v>-2.193118804283134</v>
+      </c>
+      <c r="G248" t="n">
+        <v>42.15384748519664</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -6158,6 +7650,12 @@
           <t>FRIEIRA 220</t>
         </is>
       </c>
+      <c r="F249" t="n">
+        <v>-1.64129534107808</v>
+      </c>
+      <c r="G249" t="n">
+        <v>41.95276958920449</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -6181,6 +7679,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F250" t="n">
+        <v>-1.509272741489286</v>
+      </c>
+      <c r="G250" t="n">
+        <v>42.38489163653953</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -6204,6 +7708,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F251" t="n">
+        <v>-1.125485076625873</v>
+      </c>
+      <c r="G251" t="n">
+        <v>42.39444092331676</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -6227,6 +7737,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F252" t="n">
+        <v>-1.950032962178306</v>
+      </c>
+      <c r="G252" t="n">
+        <v>42.35590492463772</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6250,6 +7766,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F253" t="n">
+        <v>-1.818887721131923</v>
+      </c>
+      <c r="G253" t="n">
+        <v>42.2901190137455</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6273,6 +7795,12 @@
           <t>FRIEIRA 220</t>
         </is>
       </c>
+      <c r="F254" t="n">
+        <v>-1.981151524649366</v>
+      </c>
+      <c r="G254" t="n">
+        <v>41.95614484521879</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6296,6 +7824,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F255" t="n">
+        <v>-1.678998547486863</v>
+      </c>
+      <c r="G255" t="n">
+        <v>42.12547419173919</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6319,6 +7853,12 @@
           <t>FRIEIRA 220</t>
         </is>
       </c>
+      <c r="F256" t="n">
+        <v>-1.465028707809272</v>
+      </c>
+      <c r="G256" t="n">
+        <v>41.93229190861292</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6342,6 +7882,12 @@
           <t>VELLE 220</t>
         </is>
       </c>
+      <c r="F257" t="n">
+        <v>-1.84877813386191</v>
+      </c>
+      <c r="G257" t="n">
+        <v>42.3578598080344</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6365,6 +7911,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F258" t="n">
+        <v>-1.706392761275467</v>
+      </c>
+      <c r="G258" t="n">
+        <v>42.0586444925318</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6388,6 +7940,12 @@
           <t>ATIOS 220</t>
         </is>
       </c>
+      <c r="F259" t="n">
+        <v>-2.621945790887332</v>
+      </c>
+      <c r="G259" t="n">
+        <v>42.13766185838121</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6411,6 +7969,12 @@
           <t>ATIOS 220</t>
         </is>
       </c>
+      <c r="F260" t="n">
+        <v>-2.735850054308774</v>
+      </c>
+      <c r="G260" t="n">
+        <v>42.21059008795999</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6434,6 +7998,12 @@
           <t>TIBO 220</t>
         </is>
       </c>
+      <c r="F261" t="n">
+        <v>-2.674860434548688</v>
+      </c>
+      <c r="G261" t="n">
+        <v>42.51990031068164</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6457,6 +8027,12 @@
           <t>PAZOS DE BORBEN 220</t>
         </is>
       </c>
+      <c r="F262" t="n">
+        <v>-2.72652684724356</v>
+      </c>
+      <c r="G262" t="n">
+        <v>42.23466911767782</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6480,6 +8056,12 @@
           <t>TIBO 220</t>
         </is>
       </c>
+      <c r="F263" t="n">
+        <v>-2.783309096530071</v>
+      </c>
+      <c r="G263" t="n">
+        <v>42.51288896071031</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6503,6 +8085,12 @@
           <t>LOURIZAN 220</t>
         </is>
       </c>
+      <c r="F264" t="n">
+        <v>-2.784100122192769</v>
+      </c>
+      <c r="G264" t="n">
+        <v>42.2896579994608</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6526,6 +8114,12 @@
           <t>ATIOS 220</t>
         </is>
       </c>
+      <c r="F265" t="n">
+        <v>-2.81080432347615</v>
+      </c>
+      <c r="G265" t="n">
+        <v>42.1129466219379</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6549,6 +8143,12 @@
           <t>CHANTADA 220</t>
         </is>
       </c>
+      <c r="F266" t="n">
+        <v>-2.111530468805121</v>
+      </c>
+      <c r="G266" t="n">
+        <v>42.65223638218523</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6572,6 +8172,12 @@
           <t>TIBO 220</t>
         </is>
       </c>
+      <c r="F267" t="n">
+        <v>-2.503891372729513</v>
+      </c>
+      <c r="G267" t="n">
+        <v>42.68498340074346</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6595,6 +8201,12 @@
           <t>LOURIZAN 220</t>
         </is>
       </c>
+      <c r="F268" t="n">
+        <v>-2.664780099388735</v>
+      </c>
+      <c r="G268" t="n">
+        <v>42.41731190342755</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6618,6 +8230,12 @@
           <t>PAZOS DE BORBEN 220</t>
         </is>
       </c>
+      <c r="F269" t="n">
+        <v>-2.644478112648293</v>
+      </c>
+      <c r="G269" t="n">
+        <v>42.21537782284174</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6641,6 +8259,12 @@
           <t>TIBO 220</t>
         </is>
       </c>
+      <c r="F270" t="n">
+        <v>-2.620412024518123</v>
+      </c>
+      <c r="G270" t="n">
+        <v>42.43818451747543</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6664,6 +8288,12 @@
           <t>PORTODEMOUROS 220</t>
         </is>
       </c>
+      <c r="F271" t="n">
+        <v>-2.349892571508382</v>
+      </c>
+      <c r="G271" t="n">
+        <v>42.76940468935944</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6687,6 +8317,12 @@
           <t>PORTODEMOUROS 220</t>
         </is>
       </c>
+      <c r="F272" t="n">
+        <v>-2.189711093422901</v>
+      </c>
+      <c r="G272" t="n">
+        <v>42.85366369255738</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6710,6 +8346,12 @@
           <t>PAZOS DE BORBEN 220</t>
         </is>
       </c>
+      <c r="F273" t="n">
+        <v>-2.613099575852009</v>
+      </c>
+      <c r="G273" t="n">
+        <v>42.35001807595149</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6733,6 +8375,12 @@
           <t>FRIEIRA 220</t>
         </is>
       </c>
+      <c r="F274" t="n">
+        <v>-2.50524092683424</v>
+      </c>
+      <c r="G274" t="n">
+        <v>42.18487973673584</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6756,6 +8404,12 @@
           <t>PAZOS DE BORBEN 220</t>
         </is>
       </c>
+      <c r="F275" t="n">
+        <v>-2.554521455418412</v>
+      </c>
+      <c r="G275" t="n">
+        <v>42.3665837727883</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6779,6 +8433,12 @@
           <t>PAZOS DE BORBEN 220</t>
         </is>
       </c>
+      <c r="F276" t="n">
+        <v>-2.590120984932759</v>
+      </c>
+      <c r="G276" t="n">
+        <v>42.26318187074592</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6802,6 +8462,12 @@
           <t>PAZOS DE BORBEN 220</t>
         </is>
       </c>
+      <c r="F277" t="n">
+        <v>-2.62300784589095</v>
+      </c>
+      <c r="G277" t="n">
+        <v>42.28481954430262</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6825,6 +8491,12 @@
           <t>ATIOS 220</t>
         </is>
       </c>
+      <c r="F278" t="n">
+        <v>-2.84811447665147</v>
+      </c>
+      <c r="G278" t="n">
+        <v>41.92784372679003</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6848,6 +8520,12 @@
           <t>ATIOS 220</t>
         </is>
       </c>
+      <c r="F279" t="n">
+        <v>-2.465341744840273</v>
+      </c>
+      <c r="G279" t="n">
+        <v>42.08962903924376</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6871,6 +8549,12 @@
           <t>LOURIZAN 220</t>
         </is>
       </c>
+      <c r="F280" t="n">
+        <v>-2.80447256239554</v>
+      </c>
+      <c r="G280" t="n">
+        <v>42.43643077989049</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6894,6 +8578,12 @@
           <t>PAZOS DE BORBEN 220</t>
         </is>
       </c>
+      <c r="F281" t="n">
+        <v>-2.699297629210959</v>
+      </c>
+      <c r="G281" t="n">
+        <v>42.21106749249508</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6917,6 +8607,12 @@
           <t>TIBO 220</t>
         </is>
       </c>
+      <c r="F282" t="n">
+        <v>-2.521854058985565</v>
+      </c>
+      <c r="G282" t="n">
+        <v>42.52306545926947</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6940,6 +8636,12 @@
           <t>TIBO 220</t>
         </is>
       </c>
+      <c r="F283" t="n">
+        <v>-2.643856813609201</v>
+      </c>
+      <c r="G283" t="n">
+        <v>42.5855503604643</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6963,6 +8665,12 @@
           <t>PAZOS DE BORBEN 220</t>
         </is>
       </c>
+      <c r="F284" t="n">
+        <v>-2.694751794129544</v>
+      </c>
+      <c r="G284" t="n">
+        <v>42.24434275778702</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6986,6 +8694,12 @@
           <t>ATIOS 220</t>
         </is>
       </c>
+      <c r="F285" t="n">
+        <v>-2.658955519901601</v>
+      </c>
+      <c r="G285" t="n">
+        <v>42.05539538509405</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -7009,6 +8723,12 @@
           <t>ATIOS 220</t>
         </is>
       </c>
+      <c r="F286" t="n">
+        <v>-2.708960823268928</v>
+      </c>
+      <c r="G286" t="n">
+        <v>42.17507601467891</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -7032,6 +8752,12 @@
           <t>TIBO 220</t>
         </is>
       </c>
+      <c r="F287" t="n">
+        <v>-2.747527130822156</v>
+      </c>
+      <c r="G287" t="n">
+        <v>42.59588509324396</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -7055,6 +8781,12 @@
           <t>LOURIZAN 220</t>
         </is>
       </c>
+      <c r="F288" t="n">
+        <v>-2.833099838253204</v>
+      </c>
+      <c r="G288" t="n">
+        <v>42.44296033466445</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -7078,6 +8810,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F289" t="n">
+        <v>-4.233755452421221</v>
+      </c>
+      <c r="G289" t="n">
+        <v>40.77946308216475</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -7101,6 +8839,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F290" t="n">
+        <v>-4.105977104420851</v>
+      </c>
+      <c r="G290" t="n">
+        <v>40.95032005592138</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -7124,6 +8868,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F291" t="n">
+        <v>-3.636277110372217</v>
+      </c>
+      <c r="G291" t="n">
+        <v>41.33888613121248</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -7147,6 +8897,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F292" t="n">
+        <v>-3.886297690587286</v>
+      </c>
+      <c r="G292" t="n">
+        <v>41.33737643585686</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -7170,6 +8926,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F293" t="n">
+        <v>-4.115332127830081</v>
+      </c>
+      <c r="G293" t="n">
+        <v>40.92516942034728</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -7193,6 +8955,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F294" t="n">
+        <v>-3.907398800573746</v>
+      </c>
+      <c r="G294" t="n">
+        <v>41.26118767252999</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -7216,6 +8984,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F295" t="n">
+        <v>-4.309410695179505</v>
+      </c>
+      <c r="G295" t="n">
+        <v>41.39476131884967</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -7239,6 +9013,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F296" t="n">
+        <v>-4.270017535604329</v>
+      </c>
+      <c r="G296" t="n">
+        <v>40.74271221195364</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -7262,6 +9042,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F297" t="n">
+        <v>-3.550245768459385</v>
+      </c>
+      <c r="G297" t="n">
+        <v>41.43218874232821</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -7285,6 +9071,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F298" t="n">
+        <v>-4.34902132101301</v>
+      </c>
+      <c r="G298" t="n">
+        <v>41.2014632851213</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7308,6 +9100,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F299" t="n">
+        <v>-4.1158857851647</v>
+      </c>
+      <c r="G299" t="n">
+        <v>41.15451516425082</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7331,6 +9129,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F300" t="n">
+        <v>-4.170922669811959</v>
+      </c>
+      <c r="G300" t="n">
+        <v>41.21875211990304</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7354,6 +9158,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F301" t="n">
+        <v>-4.006581182924822</v>
+      </c>
+      <c r="G301" t="n">
+        <v>40.90506394096379</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7377,6 +9187,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F302" t="n">
+        <v>-4.33913273921929</v>
+      </c>
+      <c r="G302" t="n">
+        <v>40.88095399657021</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7400,6 +9216,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F303" t="n">
+        <v>-4.499138274526815</v>
+      </c>
+      <c r="G303" t="n">
+        <v>41.15549671357665</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7423,6 +9245,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F304" t="n">
+        <v>-4.20711657589127</v>
+      </c>
+      <c r="G304" t="n">
+        <v>40.81224665911878</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7446,6 +9274,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F305" t="n">
+        <v>-4.154704727716366</v>
+      </c>
+      <c r="G305" t="n">
+        <v>40.9252592698684</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7469,6 +9303,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F306" t="n">
+        <v>-4.333474762912802</v>
+      </c>
+      <c r="G306" t="n">
+        <v>41.14941811298616</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7492,6 +9332,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F307" t="n">
+        <v>-3.72460171649801</v>
+      </c>
+      <c r="G307" t="n">
+        <v>41.13805816807606</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7515,6 +9361,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F308" t="n">
+        <v>-4.082507348826206</v>
+      </c>
+      <c r="G308" t="n">
+        <v>40.93476963423174</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7538,6 +9390,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F309" t="n">
+        <v>-3.494602235556792</v>
+      </c>
+      <c r="G309" t="n">
+        <v>41.27421318947518</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7561,6 +9419,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F310" t="n">
+        <v>-4.311611062032715</v>
+      </c>
+      <c r="G310" t="n">
+        <v>41.32388427114777</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7584,6 +9448,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F311" t="n">
+        <v>-4.001555950047139</v>
+      </c>
+      <c r="G311" t="n">
+        <v>41.15682718066946</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7607,6 +9477,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F312" t="n">
+        <v>-4.422139997050293</v>
+      </c>
+      <c r="G312" t="n">
+        <v>40.78210526853898</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7630,6 +9506,12 @@
           <t>LASTRAS 400</t>
         </is>
       </c>
+      <c r="F313" t="n">
+        <v>-4.19803183409315</v>
+      </c>
+      <c r="G313" t="n">
+        <v>40.95753445475184</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7653,6 +9535,12 @@
           <t>FUENTES DE LA ALCARRIA 400</t>
         </is>
       </c>
+      <c r="F314" t="n">
+        <v>-2.287765492549578</v>
+      </c>
+      <c r="G314" t="n">
+        <v>41.20966681035879</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7676,6 +9564,12 @@
           <t>ACECA 220</t>
         </is>
       </c>
+      <c r="F315" t="n">
+        <v>-3.8577777372042</v>
+      </c>
+      <c r="G315" t="n">
+        <v>39.94204494853001</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7699,6 +9593,12 @@
           <t>ACECA 220</t>
         </is>
       </c>
+      <c r="F316" t="n">
+        <v>-4.118847451782718</v>
+      </c>
+      <c r="G316" t="n">
+        <v>40.06780821008297</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7722,6 +9622,12 @@
           <t>ACECA 220</t>
         </is>
       </c>
+      <c r="F317" t="n">
+        <v>-3.756024784021635</v>
+      </c>
+      <c r="G317" t="n">
+        <v>39.9802155833395</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7745,6 +9651,12 @@
           <t>ACECA 220</t>
         </is>
       </c>
+      <c r="F318" t="n">
+        <v>-4.020718177652367</v>
+      </c>
+      <c r="G318" t="n">
+        <v>40.11472550671303</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7768,6 +9680,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F319" t="n">
+        <v>-3.449788229802628</v>
+      </c>
+      <c r="G319" t="n">
+        <v>39.97652874412683</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7791,6 +9709,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F320" t="n">
+        <v>-3.179321916379257</v>
+      </c>
+      <c r="G320" t="n">
+        <v>39.76145520914272</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7814,6 +9738,12 @@
           <t>ACECA 220</t>
         </is>
       </c>
+      <c r="F321" t="n">
+        <v>-4.474373646465389</v>
+      </c>
+      <c r="G321" t="n">
+        <v>39.85412723336205</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7837,6 +9767,12 @@
           <t>ACECA 220</t>
         </is>
       </c>
+      <c r="F322" t="n">
+        <v>-4.407536644622952</v>
+      </c>
+      <c r="G322" t="n">
+        <v>40.16629233130542</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7860,6 +9796,12 @@
           <t>ACECA 220</t>
         </is>
       </c>
+      <c r="F323" t="n">
+        <v>-4.359088794249635</v>
+      </c>
+      <c r="G323" t="n">
+        <v>40.15060077926022</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7883,6 +9825,12 @@
           <t>ACECA 220</t>
         </is>
       </c>
+      <c r="F324" t="n">
+        <v>-4.221264669768039</v>
+      </c>
+      <c r="G324" t="n">
+        <v>40.05859322448405</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7906,6 +9854,12 @@
           <t>LOS PRADILLOS 220</t>
         </is>
       </c>
+      <c r="F325" t="n">
+        <v>-3.822877411303231</v>
+      </c>
+      <c r="G325" t="n">
+        <v>40.15977071470673</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7929,6 +9883,12 @@
           <t>LOS PRADILLOS 220</t>
         </is>
       </c>
+      <c r="F326" t="n">
+        <v>-3.865430581174842</v>
+      </c>
+      <c r="G326" t="n">
+        <v>40.10046675751713</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7952,6 +9912,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F327" t="n">
+        <v>-3.369321433657923</v>
+      </c>
+      <c r="G327" t="n">
+        <v>40.00044572446575</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7975,6 +9941,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F328" t="n">
+        <v>-3.531008551815241</v>
+      </c>
+      <c r="G328" t="n">
+        <v>39.48733948637999</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7998,6 +9970,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F329" t="n">
+        <v>-3.798359204808651</v>
+      </c>
+      <c r="G329" t="n">
+        <v>39.67610848139177</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -8021,6 +9999,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F330" t="n">
+        <v>-3.417216177959896</v>
+      </c>
+      <c r="G330" t="n">
+        <v>39.97593878384597</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -8044,6 +10028,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F331" t="n">
+        <v>-3.48848942727603</v>
+      </c>
+      <c r="G331" t="n">
+        <v>39.96283039193514</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -8067,6 +10057,12 @@
           <t>ACECA 220</t>
         </is>
       </c>
+      <c r="F332" t="n">
+        <v>-3.825167801166173</v>
+      </c>
+      <c r="G332" t="n">
+        <v>40.03162141322201</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -8090,6 +10086,12 @@
           <t>LOS PRADILLOS 220</t>
         </is>
       </c>
+      <c r="F333" t="n">
+        <v>-3.819858781477401</v>
+      </c>
+      <c r="G333" t="n">
+        <v>40.13235845282237</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -8113,6 +10115,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F334" t="n">
+        <v>-3.391577766579932</v>
+      </c>
+      <c r="G334" t="n">
+        <v>39.64800807639526</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -8136,6 +10144,12 @@
           <t>LOS PRADILLOS 220</t>
         </is>
       </c>
+      <c r="F335" t="n">
+        <v>-3.974668134359989</v>
+      </c>
+      <c r="G335" t="n">
+        <v>40.04783064121934</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -8159,6 +10173,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F336" t="n">
+        <v>-3.190555117911895</v>
+      </c>
+      <c r="G336" t="n">
+        <v>39.99044415900906</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -8182,6 +10202,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F337" t="n">
+        <v>-3.676424153603767</v>
+      </c>
+      <c r="G337" t="n">
+        <v>40.11217584356562</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -8205,6 +10231,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F338" t="n">
+        <v>-3.801247843815097</v>
+      </c>
+      <c r="G338" t="n">
+        <v>39.41781621160063</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -8228,6 +10260,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F339" t="n">
+        <v>-3.36860664674697</v>
+      </c>
+      <c r="G339" t="n">
+        <v>39.41951406771518</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -8251,6 +10289,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F340" t="n">
+        <v>-3.343956676747628</v>
+      </c>
+      <c r="G340" t="n">
+        <v>39.61569457791033</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -8274,6 +10318,12 @@
           <t>ACECA 220</t>
         </is>
       </c>
+      <c r="F341" t="n">
+        <v>-4.09671211701298</v>
+      </c>
+      <c r="G341" t="n">
+        <v>40.21479040005593</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -8297,6 +10347,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F342" t="n">
+        <v>-3.745408600793595</v>
+      </c>
+      <c r="G342" t="n">
+        <v>39.89772789064235</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -8320,6 +10376,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F343" t="n">
+        <v>-3.374981628377646</v>
+      </c>
+      <c r="G343" t="n">
+        <v>39.98363331711226</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -8343,6 +10405,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F344" t="n">
+        <v>-3.789835345502842</v>
+      </c>
+      <c r="G344" t="n">
+        <v>40.12436851724048</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8366,6 +10434,12 @@
           <t>MADRIDEJOS 220</t>
         </is>
       </c>
+      <c r="F345" t="n">
+        <v>-3.855383819063058</v>
+      </c>
+      <c r="G345" t="n">
+        <v>39.57449990951481</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8389,6 +10463,12 @@
           <t>VALDEMORO 220</t>
         </is>
       </c>
+      <c r="F346" t="n">
+        <v>-3.619130893301277</v>
+      </c>
+      <c r="G346" t="n">
+        <v>39.89483083104297</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8412,6 +10492,12 @@
           <t>SAN AGUSTIN 220</t>
         </is>
       </c>
+      <c r="F347" t="n">
+        <v>-6.661213574753803</v>
+      </c>
+      <c r="G347" t="n">
+        <v>42.05978101513049</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8434,6 +10520,12 @@
         <is>
           <t>COMPOSTILLA 400</t>
         </is>
+      </c>
+      <c r="F348" t="n">
+        <v>-6.164960042834816</v>
+      </c>
+      <c r="G348" t="n">
+        <v>42.01207375971697</v>
       </c>
     </row>
   </sheetData>

--- a/Distribucion/Excels/UFD.xlsx
+++ b/Distribucion/Excels/UFD.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G348"/>
+  <dimension ref="A1:H348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>Latitud</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Comunidad</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +498,11 @@
       <c r="G2" t="n">
         <v>43.29202155679044</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
       <c r="G3" t="n">
         <v>40.42657333373005</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +566,11 @@
       <c r="G4" t="n">
         <v>40.4129319236209</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +600,11 @@
       <c r="G5" t="n">
         <v>41.31292701121468</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +634,11 @@
       <c r="G6" t="n">
         <v>38.88969896433933</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +668,11 @@
       <c r="G7" t="n">
         <v>38.71438054108086</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,6 +702,11 @@
       <c r="G8" t="n">
         <v>38.87663116446411</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,6 +736,11 @@
       <c r="G9" t="n">
         <v>39.13761781669608</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -725,6 +770,11 @@
       <c r="G10" t="n">
         <v>38.9480376638934</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -754,6 +804,11 @@
       <c r="G11" t="n">
         <v>38.77036164981274</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -783,6 +838,11 @@
       <c r="G12" t="n">
         <v>38.89102915427546</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,6 +872,11 @@
       <c r="G13" t="n">
         <v>38.87332361509112</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +906,11 @@
       <c r="G14" t="n">
         <v>38.51918028644226</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -870,6 +940,11 @@
       <c r="G15" t="n">
         <v>38.71740322779228</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -899,6 +974,11 @@
       <c r="G16" t="n">
         <v>39.37950393532849</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -928,6 +1008,11 @@
       <c r="G17" t="n">
         <v>39.41159246557578</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -957,6 +1042,11 @@
       <c r="G18" t="n">
         <v>39.17687949177368</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -986,6 +1076,11 @@
       <c r="G19" t="n">
         <v>38.70301898497836</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1015,6 +1110,11 @@
       <c r="G20" t="n">
         <v>38.97624609210852</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1044,6 +1144,11 @@
       <c r="G21" t="n">
         <v>39.39313093648841</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1073,6 +1178,11 @@
       <c r="G22" t="n">
         <v>38.67895587215097</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1102,6 +1212,11 @@
       <c r="G23" t="n">
         <v>38.67934075028865</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1131,6 +1246,11 @@
       <c r="G24" t="n">
         <v>38.85835288528049</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1160,6 +1280,11 @@
       <c r="G25" t="n">
         <v>39.07081858539385</v>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1189,6 +1314,11 @@
       <c r="G26" t="n">
         <v>39.07258204350319</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1218,6 +1348,11 @@
       <c r="G27" t="n">
         <v>39.21849095180031</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1247,6 +1382,11 @@
       <c r="G28" t="n">
         <v>38.47196374915249</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1276,6 +1416,11 @@
       <c r="G29" t="n">
         <v>39.11230766670364</v>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1305,6 +1450,11 @@
       <c r="G30" t="n">
         <v>39.17109810009563</v>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1334,6 +1484,11 @@
       <c r="G31" t="n">
         <v>39.16970433862709</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1363,6 +1518,11 @@
       <c r="G32" t="n">
         <v>39.29623480110987</v>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1392,6 +1552,11 @@
       <c r="G33" t="n">
         <v>38.8193584541234</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1421,6 +1586,11 @@
       <c r="G34" t="n">
         <v>38.56562276982844</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1450,6 +1620,11 @@
       <c r="G35" t="n">
         <v>39.00438654026506</v>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1479,6 +1654,11 @@
       <c r="G36" t="n">
         <v>39.40143697712289</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1508,6 +1688,11 @@
       <c r="G37" t="n">
         <v>39.03279089334351</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1537,6 +1722,11 @@
       <c r="G38" t="n">
         <v>39.02050695225117</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1566,6 +1756,11 @@
       <c r="G39" t="n">
         <v>39.42272532376067</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1595,6 +1790,11 @@
       <c r="G40" t="n">
         <v>39.2202821227261</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1624,6 +1824,11 @@
       <c r="G41" t="n">
         <v>38.64661113004796</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1653,6 +1858,11 @@
       <c r="G42" t="n">
         <v>39.29800385983495</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1682,6 +1892,11 @@
       <c r="G43" t="n">
         <v>38.93073666194528</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1711,6 +1926,11 @@
       <c r="G44" t="n">
         <v>39.17641349470038</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1740,6 +1960,11 @@
       <c r="G45" t="n">
         <v>38.7444173206971</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1769,6 +1994,11 @@
       <c r="G46" t="n">
         <v>38.75207613512946</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1798,6 +2028,11 @@
       <c r="G47" t="n">
         <v>38.75653710202317</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1827,6 +2062,11 @@
       <c r="G48" t="n">
         <v>39.20956978723552</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1856,6 +2096,11 @@
       <c r="G49" t="n">
         <v>40.39947041357562</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1885,6 +2130,11 @@
       <c r="G50" t="n">
         <v>40.07201181996189</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1914,6 +2164,11 @@
       <c r="G51" t="n">
         <v>40.04168284272767</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1943,6 +2198,11 @@
       <c r="G52" t="n">
         <v>40.07769631168953</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1972,6 +2232,11 @@
       <c r="G53" t="n">
         <v>39.90464976598741</v>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2001,6 +2266,11 @@
       <c r="G54" t="n">
         <v>40.31319141271813</v>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2030,6 +2300,11 @@
       <c r="G55" t="n">
         <v>40.23798778404076</v>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2059,6 +2334,11 @@
       <c r="G56" t="n">
         <v>40.59076517850762</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2088,6 +2368,11 @@
       <c r="G57" t="n">
         <v>40.26663250240857</v>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2117,6 +2402,11 @@
       <c r="G58" t="n">
         <v>40.36433415203238</v>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2146,6 +2436,11 @@
       <c r="G59" t="n">
         <v>40.72527463187998</v>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2175,6 +2470,11 @@
       <c r="G60" t="n">
         <v>40.34954744157752</v>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2204,6 +2504,11 @@
       <c r="G61" t="n">
         <v>40.57425209871404</v>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2233,6 +2538,11 @@
       <c r="G62" t="n">
         <v>40.78645354249291</v>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2262,6 +2572,11 @@
       <c r="G63" t="n">
         <v>40.49302996483427</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2291,6 +2606,11 @@
       <c r="G64" t="n">
         <v>40.6185024582289</v>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2320,6 +2640,11 @@
       <c r="G65" t="n">
         <v>40.37262240513472</v>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2349,6 +2674,11 @@
       <c r="G66" t="n">
         <v>40.63670259631445</v>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2378,6 +2708,11 @@
       <c r="G67" t="n">
         <v>40.2477778186573</v>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2407,6 +2742,11 @@
       <c r="G68" t="n">
         <v>41.04687919995176</v>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2436,6 +2776,11 @@
       <c r="G69" t="n">
         <v>40.83775483255648</v>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2465,6 +2810,11 @@
       <c r="G70" t="n">
         <v>40.58975376907742</v>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2494,6 +2844,11 @@
       <c r="G71" t="n">
         <v>40.33905490569617</v>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2503,7 +2858,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2523,6 +2878,11 @@
       <c r="G72" t="n">
         <v>43.47500810572026</v>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2532,7 +2892,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2552,6 +2912,11 @@
       <c r="G73" t="n">
         <v>43.27984396768383</v>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2561,7 +2926,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2581,6 +2946,11 @@
       <c r="G74" t="n">
         <v>43.09694375977974</v>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2590,7 +2960,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2610,6 +2980,11 @@
       <c r="G75" t="n">
         <v>42.66969401566848</v>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2619,7 +2994,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2639,6 +3014,11 @@
       <c r="G76" t="n">
         <v>43.23245265940853</v>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2648,7 +3028,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2668,6 +3048,11 @@
       <c r="G77" t="n">
         <v>43.2152617988873</v>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2677,7 +3062,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2697,6 +3082,11 @@
       <c r="G78" t="n">
         <v>43.20508788880588</v>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2706,7 +3096,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2726,6 +3116,11 @@
       <c r="G79" t="n">
         <v>43.63811475406554</v>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2735,7 +3130,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2755,6 +3150,11 @@
       <c r="G80" t="n">
         <v>43.13639179065881</v>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2764,7 +3164,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2784,6 +3184,11 @@
       <c r="G81" t="n">
         <v>43.02645068447703</v>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2793,7 +3198,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2813,6 +3218,11 @@
       <c r="G82" t="n">
         <v>43.50902804182268</v>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2822,7 +3232,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2842,6 +3252,11 @@
       <c r="G83" t="n">
         <v>43.16584869872062</v>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2851,7 +3266,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2871,6 +3286,11 @@
       <c r="G84" t="n">
         <v>43.15588163178695</v>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2880,7 +3300,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2900,6 +3320,11 @@
       <c r="G85" t="n">
         <v>43.3429952237728</v>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2909,7 +3334,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2929,6 +3354,11 @@
       <c r="G86" t="n">
         <v>43.3667085330877</v>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2938,7 +3368,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2958,6 +3388,11 @@
       <c r="G87" t="n">
         <v>43.40572455733638</v>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2967,7 +3402,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2987,6 +3422,11 @@
       <c r="G88" t="n">
         <v>42.91448981657607</v>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2996,7 +3436,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -3016,6 +3456,11 @@
       <c r="G89" t="n">
         <v>43.47448498763491</v>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3025,7 +3470,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -3045,6 +3490,11 @@
       <c r="G90" t="n">
         <v>43.34267837884101</v>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3054,7 +3504,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -3074,6 +3524,11 @@
       <c r="G91" t="n">
         <v>43.25069886284857</v>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3083,7 +3538,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -3103,6 +3558,11 @@
       <c r="G92" t="n">
         <v>43.66476411329241</v>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3112,7 +3572,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -3132,6 +3592,11 @@
       <c r="G93" t="n">
         <v>43.51332082760207</v>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3141,7 +3606,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -3161,6 +3626,11 @@
       <c r="G94" t="n">
         <v>43.16913122769822</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3170,7 +3640,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -3190,6 +3660,11 @@
       <c r="G95" t="n">
         <v>42.91203337016726</v>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3199,7 +3674,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -3219,6 +3694,11 @@
       <c r="G96" t="n">
         <v>43.16806728416135</v>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3228,7 +3708,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -3248,6 +3728,11 @@
       <c r="G97" t="n">
         <v>43.43377350401617</v>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3257,7 +3742,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -3277,6 +3762,11 @@
       <c r="G98" t="n">
         <v>43.29924499084158</v>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3286,7 +3776,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -3306,6 +3796,11 @@
       <c r="G99" t="n">
         <v>42.78498620464142</v>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3315,7 +3810,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -3335,6 +3830,11 @@
       <c r="G100" t="n">
         <v>43.05644186060967</v>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3344,7 +3844,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -3364,6 +3864,11 @@
       <c r="G101" t="n">
         <v>42.89176475443433</v>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3373,7 +3878,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -3393,6 +3898,11 @@
       <c r="G102" t="n">
         <v>42.91584098081738</v>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3402,7 +3912,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -3422,6 +3932,11 @@
       <c r="G103" t="n">
         <v>42.74162276938289</v>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3431,7 +3946,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -3451,6 +3966,11 @@
       <c r="G104" t="n">
         <v>42.72640173899076</v>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3460,7 +3980,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -3480,6 +4000,11 @@
       <c r="G105" t="n">
         <v>43.32495874830874</v>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3489,7 +4014,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -3509,6 +4034,11 @@
       <c r="G106" t="n">
         <v>43.46831076142712</v>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3518,7 +4048,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -3538,6 +4068,11 @@
       <c r="G107" t="n">
         <v>43.43965795680131</v>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3547,7 +4082,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -3567,6 +4102,11 @@
       <c r="G108" t="n">
         <v>42.57583356681521</v>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3576,7 +4116,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -3596,6 +4136,11 @@
       <c r="G109" t="n">
         <v>42.94717734094524</v>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3605,7 +4150,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -3625,6 +4170,11 @@
       <c r="G110" t="n">
         <v>43.22533276302141</v>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3634,7 +4184,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3654,6 +4204,11 @@
       <c r="G111" t="n">
         <v>43.54066208582352</v>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3663,7 +4218,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3683,6 +4238,11 @@
       <c r="G112" t="n">
         <v>42.78760107797914</v>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3692,7 +4252,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3712,6 +4272,11 @@
       <c r="G113" t="n">
         <v>43.3508622357155</v>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3721,7 +4286,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3741,6 +4306,11 @@
       <c r="G114" t="n">
         <v>43.32840797233777</v>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3750,7 +4320,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3770,6 +4340,11 @@
       <c r="G115" t="n">
         <v>42.89154990928035</v>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3779,7 +4354,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3799,6 +4374,11 @@
       <c r="G116" t="n">
         <v>43.15137999933746</v>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3808,7 +4388,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3828,6 +4408,11 @@
       <c r="G117" t="n">
         <v>42.98150156229158</v>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3837,7 +4422,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3857,6 +4442,11 @@
       <c r="G118" t="n">
         <v>43.30956877881584</v>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3866,7 +4456,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3886,6 +4476,11 @@
       <c r="G119" t="n">
         <v>43.49438864972537</v>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3895,7 +4490,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3915,6 +4510,11 @@
       <c r="G120" t="n">
         <v>42.85479997194844</v>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3924,7 +4524,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3944,6 +4544,11 @@
       <c r="G121" t="n">
         <v>43.53834885451514</v>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3953,7 +4558,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3973,6 +4578,11 @@
       <c r="G122" t="n">
         <v>43.36966761030885</v>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3982,7 +4592,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -4002,6 +4612,11 @@
       <c r="G123" t="n">
         <v>42.8325263722349</v>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4011,7 +4626,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -4031,6 +4646,11 @@
       <c r="G124" t="n">
         <v>43.43965054963625</v>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4040,7 +4660,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LA CORUÑA</t>
+          <t>A CORUÑA</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -4060,6 +4680,11 @@
       <c r="G125" t="n">
         <v>43.1011629158779</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4089,6 +4714,11 @@
       <c r="G126" t="n">
         <v>42.59723915765961</v>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4118,6 +4748,11 @@
       <c r="G127" t="n">
         <v>42.76171315084262</v>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4147,6 +4782,11 @@
       <c r="G128" t="n">
         <v>42.4641201119811</v>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4176,6 +4816,11 @@
       <c r="G129" t="n">
         <v>42.29484626737356</v>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4205,6 +4850,11 @@
       <c r="G130" t="n">
         <v>42.61184367756623</v>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4234,6 +4884,11 @@
       <c r="G131" t="n">
         <v>42.56432939536405</v>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4263,6 +4918,11 @@
       <c r="G132" t="n">
         <v>42.48997941918184</v>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4292,6 +4952,11 @@
       <c r="G133" t="n">
         <v>42.57559356519173</v>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4321,6 +4986,11 @@
       <c r="G134" t="n">
         <v>42.61749976169468</v>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4350,6 +5020,11 @@
       <c r="G135" t="n">
         <v>42.27796238783072</v>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4379,6 +5054,11 @@
       <c r="G136" t="n">
         <v>42.69374479172913</v>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4408,6 +5088,11 @@
       <c r="G137" t="n">
         <v>42.75977110250703</v>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4437,6 +5122,11 @@
       <c r="G138" t="n">
         <v>42.45711660513202</v>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4466,6 +5156,11 @@
       <c r="G139" t="n">
         <v>42.24706670720717</v>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4495,6 +5190,11 @@
       <c r="G140" t="n">
         <v>42.56895072482293</v>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4524,6 +5224,11 @@
       <c r="G141" t="n">
         <v>42.75387945677458</v>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4553,6 +5258,11 @@
       <c r="G142" t="n">
         <v>42.56073204066423</v>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4582,6 +5292,11 @@
       <c r="G143" t="n">
         <v>42.62021944495033</v>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4611,6 +5326,11 @@
       <c r="G144" t="n">
         <v>42.79460818413451</v>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4640,6 +5360,11 @@
       <c r="G145" t="n">
         <v>42.82263479330186</v>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4669,6 +5394,11 @@
       <c r="G146" t="n">
         <v>42.41579772047478</v>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4698,6 +5428,11 @@
       <c r="G147" t="n">
         <v>42.35758821429417</v>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4727,6 +5462,11 @@
       <c r="G148" t="n">
         <v>42.93940065389307</v>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4756,6 +5496,11 @@
       <c r="G149" t="n">
         <v>42.59971464830666</v>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4785,6 +5530,11 @@
       <c r="G150" t="n">
         <v>42.53144846322846</v>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4814,6 +5564,11 @@
       <c r="G151" t="n">
         <v>42.5630365058289</v>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4843,6 +5598,11 @@
       <c r="G152" t="n">
         <v>42.62643782236754</v>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4872,6 +5632,11 @@
       <c r="G153" t="n">
         <v>42.6254581272887</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4901,6 +5666,11 @@
       <c r="G154" t="n">
         <v>42.92547519239591</v>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4930,6 +5700,11 @@
       <c r="G155" t="n">
         <v>43.12370188347003</v>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4959,6 +5734,11 @@
       <c r="G156" t="n">
         <v>43.02017378502241</v>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4988,6 +5768,11 @@
       <c r="G157" t="n">
         <v>43.01842584088055</v>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5017,6 +5802,11 @@
       <c r="G158" t="n">
         <v>42.51128702634079</v>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5046,6 +5836,11 @@
       <c r="G159" t="n">
         <v>42.79724179482108</v>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5075,6 +5870,11 @@
       <c r="G160" t="n">
         <v>42.86631143036445</v>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5104,6 +5904,11 @@
       <c r="G161" t="n">
         <v>42.46767617154996</v>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5133,6 +5938,11 @@
       <c r="G162" t="n">
         <v>42.77632059449685</v>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5162,6 +5972,11 @@
       <c r="G163" t="n">
         <v>42.75889770989652</v>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5191,6 +6006,11 @@
       <c r="G164" t="n">
         <v>40.50956406030083</v>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5220,6 +6040,11 @@
       <c r="G165" t="n">
         <v>40.47756505524588</v>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5249,6 +6074,11 @@
       <c r="G166" t="n">
         <v>40.51095669583575</v>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5278,6 +6108,11 @@
       <c r="G167" t="n">
         <v>40.4453810005067</v>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5307,6 +6142,11 @@
       <c r="G168" t="n">
         <v>40.30151933435215</v>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5336,6 +6176,11 @@
       <c r="G169" t="n">
         <v>40.27108073806115</v>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5365,6 +6210,11 @@
       <c r="G170" t="n">
         <v>40.02487007308213</v>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5394,6 +6244,11 @@
       <c r="G171" t="n">
         <v>40.45274586929609</v>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5423,6 +6278,11 @@
       <c r="G172" t="n">
         <v>40.42822728009357</v>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5452,6 +6312,11 @@
       <c r="G173" t="n">
         <v>40.41313271861819</v>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5481,6 +6346,11 @@
       <c r="G174" t="n">
         <v>40.37619332238332</v>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5510,6 +6380,11 @@
       <c r="G175" t="n">
         <v>40.36337611788599</v>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5539,6 +6414,11 @@
       <c r="G176" t="n">
         <v>40.43319761471844</v>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5568,6 +6448,11 @@
       <c r="G177" t="n">
         <v>40.11061463926556</v>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5597,6 +6482,11 @@
       <c r="G178" t="n">
         <v>40.03153186531861</v>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5626,6 +6516,11 @@
       <c r="G179" t="n">
         <v>40.4549647650618</v>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5655,6 +6550,11 @@
       <c r="G180" t="n">
         <v>40.43954308739287</v>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5684,6 +6584,11 @@
       <c r="G181" t="n">
         <v>40.43468505238382</v>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5713,6 +6618,11 @@
       <c r="G182" t="n">
         <v>40.39673330446531</v>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5742,6 +6652,11 @@
       <c r="G183" t="n">
         <v>40.42250072032943</v>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5771,6 +6686,11 @@
       <c r="G184" t="n">
         <v>40.45014830804526</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5800,6 +6720,11 @@
       <c r="G185" t="n">
         <v>40.46450348554053</v>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5829,6 +6754,11 @@
       <c r="G186" t="n">
         <v>40.38738300720381</v>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5858,6 +6788,11 @@
       <c r="G187" t="n">
         <v>40.399785309474</v>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5887,6 +6822,11 @@
       <c r="G188" t="n">
         <v>40.44526122190692</v>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5916,6 +6856,11 @@
       <c r="G189" t="n">
         <v>40.31831291778062</v>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5945,6 +6890,11 @@
       <c r="G190" t="n">
         <v>40.4727336349738</v>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5974,6 +6924,11 @@
       <c r="G191" t="n">
         <v>40.4317076528886</v>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6003,6 +6958,11 @@
       <c r="G192" t="n">
         <v>40.4942644295235</v>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6032,6 +6992,11 @@
       <c r="G193" t="n">
         <v>40.4423613224911</v>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6061,6 +7026,11 @@
       <c r="G194" t="n">
         <v>40.3877525528141</v>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6090,6 +7060,11 @@
       <c r="G195" t="n">
         <v>40.3300947763623</v>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6119,6 +7094,11 @@
       <c r="G196" t="n">
         <v>40.13183355340878</v>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6148,6 +7128,11 @@
       <c r="G197" t="n">
         <v>40.41253132996014</v>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6177,6 +7162,11 @@
       <c r="G198" t="n">
         <v>40.43423970424779</v>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6206,6 +7196,11 @@
       <c r="G199" t="n">
         <v>40.40986385482613</v>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6235,6 +7230,11 @@
       <c r="G200" t="n">
         <v>40.39055429147396</v>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6264,6 +7264,11 @@
       <c r="G201" t="n">
         <v>40.36551481736337</v>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6293,6 +7298,11 @@
       <c r="G202" t="n">
         <v>40.34024076566488</v>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6322,6 +7332,11 @@
       <c r="G203" t="n">
         <v>40.40214891216787</v>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6351,6 +7366,11 @@
       <c r="G204" t="n">
         <v>40.47547210504633</v>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6380,6 +7400,11 @@
       <c r="G205" t="n">
         <v>40.37575927893204</v>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6409,6 +7434,11 @@
       <c r="G206" t="n">
         <v>40.44543830434013</v>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6438,6 +7468,11 @@
       <c r="G207" t="n">
         <v>40.43024682225244</v>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6467,6 +7502,11 @@
       <c r="G208" t="n">
         <v>40.41246687340204</v>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6496,6 +7536,11 @@
       <c r="G209" t="n">
         <v>40.4012831068146</v>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6525,6 +7570,11 @@
       <c r="G210" t="n">
         <v>40.38846243610882</v>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6554,6 +7604,11 @@
       <c r="G211" t="n">
         <v>40.48176129305326</v>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6583,6 +7638,11 @@
       <c r="G212" t="n">
         <v>40.32148518446506</v>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6612,6 +7672,11 @@
       <c r="G213" t="n">
         <v>40.23474653842025</v>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6641,6 +7706,11 @@
       <c r="G214" t="n">
         <v>40.38385107563279</v>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6670,6 +7740,11 @@
       <c r="G215" t="n">
         <v>40.44271992042773</v>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6699,6 +7774,11 @@
       <c r="G216" t="n">
         <v>40.42487566977773</v>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6728,6 +7808,11 @@
       <c r="G217" t="n">
         <v>40.44958824440307</v>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6757,6 +7842,11 @@
       <c r="G218" t="n">
         <v>40.23122772807787</v>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6786,6 +7876,11 @@
       <c r="G219" t="n">
         <v>40.45338113929758</v>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6815,6 +7910,11 @@
       <c r="G220" t="n">
         <v>40.42355758599289</v>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6844,6 +7944,11 @@
       <c r="G221" t="n">
         <v>40.41556885000455</v>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6873,6 +7978,11 @@
       <c r="G222" t="n">
         <v>40.42451862067425</v>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6902,6 +8012,11 @@
       <c r="G223" t="n">
         <v>40.38419529039483</v>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6931,6 +8046,11 @@
       <c r="G224" t="n">
         <v>40.42454930202416</v>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6960,6 +8080,11 @@
       <c r="G225" t="n">
         <v>40.43253455134089</v>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6989,6 +8114,11 @@
       <c r="G226" t="n">
         <v>40.37217409551258</v>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7018,6 +8148,11 @@
       <c r="G227" t="n">
         <v>40.21372137076589</v>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7047,6 +8182,11 @@
       <c r="G228" t="n">
         <v>40.23535592312901</v>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7076,6 +8216,11 @@
       <c r="G229" t="n">
         <v>40.3888707021576</v>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7105,6 +8250,11 @@
       <c r="G230" t="n">
         <v>40.35049788136005</v>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7134,6 +8284,11 @@
       <c r="G231" t="n">
         <v>40.33759425287283</v>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7163,6 +8318,11 @@
       <c r="G232" t="n">
         <v>40.48690242641074</v>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7192,6 +8352,11 @@
       <c r="G233" t="n">
         <v>40.39695045089667</v>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7221,6 +8386,11 @@
       <c r="G234" t="n">
         <v>40.16334313621518</v>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7250,6 +8420,11 @@
       <c r="G235" t="n">
         <v>40.19356618739948</v>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7279,6 +8454,11 @@
       <c r="G236" t="n">
         <v>40.34836543310954</v>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7308,6 +8488,11 @@
       <c r="G237" t="n">
         <v>40.17848108203169</v>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7337,6 +8522,11 @@
       <c r="G238" t="n">
         <v>40.36376200043104</v>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7346,7 +8536,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -7366,6 +8556,11 @@
       <c r="G239" t="n">
         <v>42.39795346412646</v>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7375,7 +8570,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -7395,6 +8590,11 @@
       <c r="G240" t="n">
         <v>42.18278182147874</v>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7404,7 +8604,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -7424,6 +8624,11 @@
       <c r="G241" t="n">
         <v>42.33619342330225</v>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7433,7 +8638,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -7453,6 +8658,11 @@
       <c r="G242" t="n">
         <v>42.4183605612434</v>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7462,7 +8672,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -7482,6 +8692,11 @@
       <c r="G243" t="n">
         <v>42.2916510045028</v>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7491,7 +8706,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -7511,6 +8726,11 @@
       <c r="G244" t="n">
         <v>41.94101731784708</v>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7520,7 +8740,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -7540,6 +8760,11 @@
       <c r="G245" t="n">
         <v>42.14602636633268</v>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7549,7 +8774,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -7569,6 +8794,11 @@
       <c r="G246" t="n">
         <v>42.43603699374314</v>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7578,7 +8808,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -7598,6 +8828,11 @@
       <c r="G247" t="n">
         <v>42.38874939169047</v>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7607,7 +8842,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -7627,6 +8862,11 @@
       <c r="G248" t="n">
         <v>42.15384748519664</v>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7636,7 +8876,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -7656,6 +8896,11 @@
       <c r="G249" t="n">
         <v>41.95276958920449</v>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7665,7 +8910,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -7685,6 +8930,11 @@
       <c r="G250" t="n">
         <v>42.38489163653953</v>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7694,7 +8944,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -7714,6 +8964,11 @@
       <c r="G251" t="n">
         <v>42.39444092331676</v>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -7723,7 +8978,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -7743,6 +8998,11 @@
       <c r="G252" t="n">
         <v>42.35590492463772</v>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -7752,7 +9012,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -7772,6 +9032,11 @@
       <c r="G253" t="n">
         <v>42.2901190137455</v>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -7781,7 +9046,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -7801,6 +9066,11 @@
       <c r="G254" t="n">
         <v>41.95614484521879</v>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -7810,7 +9080,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -7830,6 +9100,11 @@
       <c r="G255" t="n">
         <v>42.12547419173919</v>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7839,7 +9114,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -7859,6 +9134,11 @@
       <c r="G256" t="n">
         <v>41.93229190861292</v>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7868,7 +9148,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -7888,6 +9168,11 @@
       <c r="G257" t="n">
         <v>42.3578598080344</v>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -7897,7 +9182,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>ORENSE</t>
+          <t>OURENSE</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -7917,6 +9202,11 @@
       <c r="G258" t="n">
         <v>42.0586444925318</v>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -7946,6 +9236,11 @@
       <c r="G259" t="n">
         <v>42.13766185838121</v>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -7975,6 +9270,11 @@
       <c r="G260" t="n">
         <v>42.21059008795999</v>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8004,6 +9304,11 @@
       <c r="G261" t="n">
         <v>42.51990031068164</v>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8033,6 +9338,11 @@
       <c r="G262" t="n">
         <v>42.23466911767782</v>
       </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8062,6 +9372,11 @@
       <c r="G263" t="n">
         <v>42.51288896071031</v>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8091,6 +9406,11 @@
       <c r="G264" t="n">
         <v>42.2896579994608</v>
       </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8120,6 +9440,11 @@
       <c r="G265" t="n">
         <v>42.1129466219379</v>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8149,6 +9474,11 @@
       <c r="G266" t="n">
         <v>42.65223638218523</v>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8178,6 +9508,11 @@
       <c r="G267" t="n">
         <v>42.68498340074346</v>
       </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8207,6 +9542,11 @@
       <c r="G268" t="n">
         <v>42.41731190342755</v>
       </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8236,6 +9576,11 @@
       <c r="G269" t="n">
         <v>42.21537782284174</v>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8265,6 +9610,11 @@
       <c r="G270" t="n">
         <v>42.43818451747543</v>
       </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8294,6 +9644,11 @@
       <c r="G271" t="n">
         <v>42.76940468935944</v>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8323,6 +9678,11 @@
       <c r="G272" t="n">
         <v>42.85366369255738</v>
       </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8352,6 +9712,11 @@
       <c r="G273" t="n">
         <v>42.35001807595149</v>
       </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8381,6 +9746,11 @@
       <c r="G274" t="n">
         <v>42.18487973673584</v>
       </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8410,6 +9780,11 @@
       <c r="G275" t="n">
         <v>42.3665837727883</v>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8439,6 +9814,11 @@
       <c r="G276" t="n">
         <v>42.26318187074592</v>
       </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8468,6 +9848,11 @@
       <c r="G277" t="n">
         <v>42.28481954430262</v>
       </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8497,6 +9882,11 @@
       <c r="G278" t="n">
         <v>41.92784372679003</v>
       </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8526,6 +9916,11 @@
       <c r="G279" t="n">
         <v>42.08962903924376</v>
       </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -8555,6 +9950,11 @@
       <c r="G280" t="n">
         <v>42.43643077989049</v>
       </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8584,6 +9984,11 @@
       <c r="G281" t="n">
         <v>42.21106749249508</v>
       </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8613,6 +10018,11 @@
       <c r="G282" t="n">
         <v>42.52306545926947</v>
       </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8642,6 +10052,11 @@
       <c r="G283" t="n">
         <v>42.5855503604643</v>
       </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -8671,6 +10086,11 @@
       <c r="G284" t="n">
         <v>42.24434275778702</v>
       </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -8700,6 +10120,11 @@
       <c r="G285" t="n">
         <v>42.05539538509405</v>
       </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -8729,6 +10154,11 @@
       <c r="G286" t="n">
         <v>42.17507601467891</v>
       </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -8758,6 +10188,11 @@
       <c r="G287" t="n">
         <v>42.59588509324396</v>
       </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -8787,6 +10222,11 @@
       <c r="G288" t="n">
         <v>42.44296033466445</v>
       </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -8816,6 +10256,11 @@
       <c r="G289" t="n">
         <v>40.77946308216475</v>
       </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -8845,6 +10290,11 @@
       <c r="G290" t="n">
         <v>40.95032005592138</v>
       </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -8874,6 +10324,11 @@
       <c r="G291" t="n">
         <v>41.33888613121248</v>
       </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -8903,6 +10358,11 @@
       <c r="G292" t="n">
         <v>41.33737643585686</v>
       </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -8932,6 +10392,11 @@
       <c r="G293" t="n">
         <v>40.92516942034728</v>
       </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -8961,6 +10426,11 @@
       <c r="G294" t="n">
         <v>41.26118767252999</v>
       </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -8990,6 +10460,11 @@
       <c r="G295" t="n">
         <v>41.39476131884967</v>
       </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9019,6 +10494,11 @@
       <c r="G296" t="n">
         <v>40.74271221195364</v>
       </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9048,6 +10528,11 @@
       <c r="G297" t="n">
         <v>41.43218874232821</v>
       </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9077,6 +10562,11 @@
       <c r="G298" t="n">
         <v>41.2014632851213</v>
       </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9106,6 +10596,11 @@
       <c r="G299" t="n">
         <v>41.15451516425082</v>
       </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -9135,6 +10630,11 @@
       <c r="G300" t="n">
         <v>41.21875211990304</v>
       </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -9164,6 +10664,11 @@
       <c r="G301" t="n">
         <v>40.90506394096379</v>
       </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -9193,6 +10698,11 @@
       <c r="G302" t="n">
         <v>40.88095399657021</v>
       </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -9222,6 +10732,11 @@
       <c r="G303" t="n">
         <v>41.15549671357665</v>
       </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -9251,6 +10766,11 @@
       <c r="G304" t="n">
         <v>40.81224665911878</v>
       </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -9280,6 +10800,11 @@
       <c r="G305" t="n">
         <v>40.9252592698684</v>
       </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -9309,6 +10834,11 @@
       <c r="G306" t="n">
         <v>41.14941811298616</v>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -9338,6 +10868,11 @@
       <c r="G307" t="n">
         <v>41.13805816807606</v>
       </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -9367,6 +10902,11 @@
       <c r="G308" t="n">
         <v>40.93476963423174</v>
       </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -9396,6 +10936,11 @@
       <c r="G309" t="n">
         <v>41.27421318947518</v>
       </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -9425,6 +10970,11 @@
       <c r="G310" t="n">
         <v>41.32388427114777</v>
       </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -9454,6 +11004,11 @@
       <c r="G311" t="n">
         <v>41.15682718066946</v>
       </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -9483,6 +11038,11 @@
       <c r="G312" t="n">
         <v>40.78210526853898</v>
       </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -9512,6 +11072,11 @@
       <c r="G313" t="n">
         <v>40.95753445475184</v>
       </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -9541,6 +11106,11 @@
       <c r="G314" t="n">
         <v>41.20966681035879</v>
       </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -9570,6 +11140,11 @@
       <c r="G315" t="n">
         <v>39.94204494853001</v>
       </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -9599,6 +11174,11 @@
       <c r="G316" t="n">
         <v>40.06780821008297</v>
       </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -9628,6 +11208,11 @@
       <c r="G317" t="n">
         <v>39.9802155833395</v>
       </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -9657,6 +11242,11 @@
       <c r="G318" t="n">
         <v>40.11472550671303</v>
       </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -9686,6 +11276,11 @@
       <c r="G319" t="n">
         <v>39.97652874412683</v>
       </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -9715,6 +11310,11 @@
       <c r="G320" t="n">
         <v>39.76145520914272</v>
       </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -9744,6 +11344,11 @@
       <c r="G321" t="n">
         <v>39.85412723336205</v>
       </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -9773,6 +11378,11 @@
       <c r="G322" t="n">
         <v>40.16629233130542</v>
       </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -9802,6 +11412,11 @@
       <c r="G323" t="n">
         <v>40.15060077926022</v>
       </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -9831,6 +11446,11 @@
       <c r="G324" t="n">
         <v>40.05859322448405</v>
       </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -9860,6 +11480,11 @@
       <c r="G325" t="n">
         <v>40.15977071470673</v>
       </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -9889,6 +11514,11 @@
       <c r="G326" t="n">
         <v>40.10046675751713</v>
       </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -9918,6 +11548,11 @@
       <c r="G327" t="n">
         <v>40.00044572446575</v>
       </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -9947,6 +11582,11 @@
       <c r="G328" t="n">
         <v>39.48733948637999</v>
       </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -9976,6 +11616,11 @@
       <c r="G329" t="n">
         <v>39.67610848139177</v>
       </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10005,6 +11650,11 @@
       <c r="G330" t="n">
         <v>39.97593878384597</v>
       </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10034,6 +11684,11 @@
       <c r="G331" t="n">
         <v>39.96283039193514</v>
       </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -10063,6 +11718,11 @@
       <c r="G332" t="n">
         <v>40.03162141322201</v>
       </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -10092,6 +11752,11 @@
       <c r="G333" t="n">
         <v>40.13235845282237</v>
       </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -10121,6 +11786,11 @@
       <c r="G334" t="n">
         <v>39.64800807639526</v>
       </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -10150,6 +11820,11 @@
       <c r="G335" t="n">
         <v>40.04783064121934</v>
       </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -10179,6 +11854,11 @@
       <c r="G336" t="n">
         <v>39.99044415900906</v>
       </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -10208,6 +11888,11 @@
       <c r="G337" t="n">
         <v>40.11217584356562</v>
       </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -10237,6 +11922,11 @@
       <c r="G338" t="n">
         <v>39.41781621160063</v>
       </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -10266,6 +11956,11 @@
       <c r="G339" t="n">
         <v>39.41951406771518</v>
       </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -10295,6 +11990,11 @@
       <c r="G340" t="n">
         <v>39.61569457791033</v>
       </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -10324,6 +12024,11 @@
       <c r="G341" t="n">
         <v>40.21479040005593</v>
       </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -10353,6 +12058,11 @@
       <c r="G342" t="n">
         <v>39.89772789064235</v>
       </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -10382,6 +12092,11 @@
       <c r="G343" t="n">
         <v>39.98363331711226</v>
       </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -10411,6 +12126,11 @@
       <c r="G344" t="n">
         <v>40.12436851724048</v>
       </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -10440,6 +12160,11 @@
       <c r="G345" t="n">
         <v>39.57449990951481</v>
       </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -10469,6 +12194,11 @@
       <c r="G346" t="n">
         <v>39.89483083104297</v>
       </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -10498,6 +12228,11 @@
       <c r="G347" t="n">
         <v>42.05978101513049</v>
       </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -10526,6 +12261,11 @@
       </c>
       <c r="G348" t="n">
         <v>42.01207375971697</v>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Distribucion/Excels/UFD.xlsx
+++ b/Distribucion/Excels/UFD.xlsx
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>-1.713381094336294</v>
+        <v>-7.713381094336302</v>
       </c>
       <c r="G152" t="n">
         <v>42.62643782236754</v>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>-1.768447803816246</v>
+        <v>-7.768447803816255</v>
       </c>
       <c r="G153" t="n">
         <v>42.6254581272887</v>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>-1.359797716940234</v>
+        <v>-7.359797716940244</v>
       </c>
       <c r="G154" t="n">
         <v>42.92547519239591</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>-1.644123379212722</v>
+        <v>-7.644123379212731</v>
       </c>
       <c r="G155" t="n">
         <v>43.12370188347003</v>
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>-1.8170406629779</v>
+        <v>-7.817040662977908</v>
       </c>
       <c r="G156" t="n">
         <v>43.02017378502241</v>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>-1.573681207817912</v>
+        <v>-7.57368120781792</v>
       </c>
       <c r="G157" t="n">
         <v>43.01842584088055</v>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>-1.513478093681456</v>
+        <v>-7.513478093681464</v>
       </c>
       <c r="G158" t="n">
         <v>42.51128702634079</v>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>-1.247254582479423</v>
+        <v>-7.247254582479431</v>
       </c>
       <c r="G159" t="n">
         <v>42.79724179482108</v>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>-1.868485986668582</v>
+        <v>-7.86848598666859</v>
       </c>
       <c r="G160" t="n">
         <v>42.86631143036445</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>-1.726928488720461</v>
+        <v>-7.726928488720469</v>
       </c>
       <c r="G161" t="n">
         <v>42.46767617154996</v>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>-1.423614127886524</v>
+        <v>-7.423614127886533</v>
       </c>
       <c r="G162" t="n">
         <v>42.77632059449685</v>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>-1.227927718559496</v>
+        <v>-7.227927718559505</v>
       </c>
       <c r="G163" t="n">
         <v>42.75889770989652</v>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>-2.621945790887332</v>
+        <v>-8.62194579088734</v>
       </c>
       <c r="G259" t="n">
         <v>42.13766185838121</v>
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>-2.735850054308774</v>
+        <v>-8.735850054308784</v>
       </c>
       <c r="G260" t="n">
         <v>42.21059008795999</v>
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>-2.674860434548688</v>
+        <v>-8.674860434548696</v>
       </c>
       <c r="G261" t="n">
         <v>42.51990031068164</v>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>-2.72652684724356</v>
+        <v>-8.726526847243569</v>
       </c>
       <c r="G262" t="n">
         <v>42.23466911767782</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>-2.783309096530071</v>
+        <v>-8.783309096530079</v>
       </c>
       <c r="G263" t="n">
         <v>42.51288896071031</v>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>-2.784100122192769</v>
+        <v>-8.784100122192777</v>
       </c>
       <c r="G264" t="n">
         <v>42.2896579994608</v>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>-2.81080432347615</v>
+        <v>-8.810804323476161</v>
       </c>
       <c r="G265" t="n">
         <v>42.1129466219379</v>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>-2.111530468805121</v>
+        <v>-8.11153046880513</v>
       </c>
       <c r="G266" t="n">
         <v>42.65223638218523</v>
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>-2.503891372729513</v>
+        <v>-8.503891372729523</v>
       </c>
       <c r="G267" t="n">
         <v>42.68498340074346</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>-2.664780099388735</v>
+        <v>-8.664780099388743</v>
       </c>
       <c r="G268" t="n">
         <v>42.41731190342755</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>-2.644478112648293</v>
+        <v>-8.644478112648301</v>
       </c>
       <c r="G269" t="n">
         <v>42.21537782284174</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>-2.620412024518123</v>
+        <v>-8.620412024518131</v>
       </c>
       <c r="G270" t="n">
         <v>42.43818451747543</v>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>-2.349892571508382</v>
+        <v>-8.34989257150839</v>
       </c>
       <c r="G271" t="n">
         <v>42.76940468935944</v>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>-2.189711093422901</v>
+        <v>-8.189711093422909</v>
       </c>
       <c r="G272" t="n">
         <v>42.85366369255738</v>
@@ -9707,7 +9707,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>-2.613099575852009</v>
+        <v>-8.613099575852017</v>
       </c>
       <c r="G273" t="n">
         <v>42.35001807595149</v>
@@ -9741,7 +9741,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>-2.50524092683424</v>
+        <v>-8.505240926834247</v>
       </c>
       <c r="G274" t="n">
         <v>42.18487973673584</v>
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>-2.554521455418412</v>
+        <v>-8.554521455418421</v>
       </c>
       <c r="G275" t="n">
         <v>42.3665837727883</v>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>-2.590120984932759</v>
+        <v>-8.590120984932767</v>
       </c>
       <c r="G276" t="n">
         <v>42.26318187074592</v>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>-2.62300784589095</v>
+        <v>-8.623007845890958</v>
       </c>
       <c r="G277" t="n">
         <v>42.28481954430262</v>
@@ -9877,7 +9877,7 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>-2.84811447665147</v>
+        <v>-8.848114476651478</v>
       </c>
       <c r="G278" t="n">
         <v>41.92784372679003</v>
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>-2.465341744840273</v>
+        <v>-8.465341744840281</v>
       </c>
       <c r="G279" t="n">
         <v>42.08962903924376</v>
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>-2.80447256239554</v>
+        <v>-8.804472562395548</v>
       </c>
       <c r="G280" t="n">
         <v>42.43643077989049</v>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>-2.699297629210959</v>
+        <v>-8.699297629210967</v>
       </c>
       <c r="G281" t="n">
         <v>42.21106749249508</v>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>-2.521854058985565</v>
+        <v>-8.521854058985573</v>
       </c>
       <c r="G282" t="n">
         <v>42.52306545926947</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>-2.643856813609201</v>
+        <v>-8.64385681360921</v>
       </c>
       <c r="G283" t="n">
         <v>42.5855503604643</v>
@@ -10081,7 +10081,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>-2.694751794129544</v>
+        <v>-8.694751794129552</v>
       </c>
       <c r="G284" t="n">
         <v>42.24434275778702</v>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>-2.658955519901601</v>
+        <v>-8.65895551990161</v>
       </c>
       <c r="G285" t="n">
         <v>42.05539538509405</v>
@@ -10149,7 +10149,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>-2.708960823268928</v>
+        <v>-8.708960823268937</v>
       </c>
       <c r="G286" t="n">
         <v>42.17507601467891</v>
@@ -10183,7 +10183,7 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>-2.747527130822156</v>
+        <v>-8.747527130822164</v>
       </c>
       <c r="G287" t="n">
         <v>42.59588509324396</v>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>-2.833099838253204</v>
+        <v>-8.833099838253212</v>
       </c>
       <c r="G288" t="n">
         <v>42.44296033466445</v>

--- a/Distribucion/Excels/UFD.xlsx
+++ b/Distribucion/Excels/UFD.xlsx
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>-2.174211171467115</v>
+        <v>-8.174211171467123</v>
       </c>
       <c r="G72" t="n">
         <v>43.47500810572026</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>-2.240192144041855</v>
+        <v>-8.240192144041863</v>
       </c>
       <c r="G73" t="n">
         <v>43.27984396768383</v>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>-2.774502628858523</v>
+        <v>-8.774502628858531</v>
       </c>
       <c r="G74" t="n">
         <v>43.09694375977974</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>-2.871045447463434</v>
+        <v>-8.871045447463443</v>
       </c>
       <c r="G75" t="n">
         <v>42.66969401566848</v>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>-2.68160272353976</v>
+        <v>-8.681602723539768</v>
       </c>
       <c r="G76" t="n">
         <v>43.23245265940853</v>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>-2.886104025481511</v>
+        <v>-8.886104025481519</v>
       </c>
       <c r="G77" t="n">
         <v>43.2152617988873</v>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>-2.68508100479393</v>
+        <v>-8.68508100479394</v>
       </c>
       <c r="G78" t="n">
         <v>43.20508788880588</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>-2.037875006717189</v>
+        <v>-8.037875006717197</v>
       </c>
       <c r="G79" t="n">
         <v>43.63811475406554</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>-2.155678559161327</v>
+        <v>-8.155678559161336</v>
       </c>
       <c r="G80" t="n">
         <v>43.13639179065881</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>-2.792472124349327</v>
+        <v>-8.792472124349336</v>
       </c>
       <c r="G81" t="n">
         <v>43.02645068447703</v>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>-2.169491784807053</v>
+        <v>-8.169491784807061</v>
       </c>
       <c r="G82" t="n">
         <v>43.50902804182268</v>
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>-2.925131125855081</v>
+        <v>-8.92513112585509</v>
       </c>
       <c r="G83" t="n">
         <v>43.16584869872062</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>-3.173316750723833</v>
+        <v>-9.173316750723842</v>
       </c>
       <c r="G84" t="n">
         <v>43.15588163178695</v>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>-2.397867553555295</v>
+        <v>-8.397867553555303</v>
       </c>
       <c r="G85" t="n">
         <v>43.3429952237728</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>-2.402150321917203</v>
+        <v>-8.402150321917212</v>
       </c>
       <c r="G86" t="n">
         <v>43.3667085330877</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>-2.044216515493278</v>
+        <v>-8.044216515493288</v>
       </c>
       <c r="G87" t="n">
         <v>43.40572455733638</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>-2.494580881167854</v>
+        <v>-8.494580881167861</v>
       </c>
       <c r="G88" t="n">
         <v>42.91448981657607</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>-2.039251087391115</v>
+        <v>-8.039251087391124</v>
       </c>
       <c r="G89" t="n">
         <v>43.47448498763491</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>-2.42914606085572</v>
+        <v>-8.429146060855729</v>
       </c>
       <c r="G90" t="n">
         <v>43.34267837884101</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>-2.579298052207804</v>
+        <v>-8.579298052207813</v>
       </c>
       <c r="G91" t="n">
         <v>43.25069886284857</v>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>-1.891476985680837</v>
+        <v>-7.891476985680846</v>
       </c>
       <c r="G92" t="n">
         <v>43.66476411329241</v>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>-2.163011794701776</v>
+        <v>-8.163011794701783</v>
       </c>
       <c r="G93" t="n">
         <v>43.51332082760207</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>-2.409555530265396</v>
+        <v>-8.409555530265404</v>
       </c>
       <c r="G94" t="n">
         <v>43.16913122769822</v>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>-2.034987142553175</v>
+        <v>-8.034987142553183</v>
       </c>
       <c r="G95" t="n">
         <v>42.91203337016726</v>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>-2.355891201124099</v>
+        <v>-8.355891201124107</v>
       </c>
       <c r="G96" t="n">
         <v>43.16806728416135</v>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>-1.854174842692247</v>
+        <v>-7.854174842692255</v>
       </c>
       <c r="G97" t="n">
         <v>43.43377350401617</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>-2.487139675594317</v>
+        <v>-8.487139675594324</v>
       </c>
       <c r="G98" t="n">
         <v>43.29924499084158</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>-3.074212650517391</v>
+        <v>-9.074212650517399</v>
       </c>
       <c r="G99" t="n">
         <v>42.78498620464142</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>-3.233269457741351</v>
+        <v>-9.233269457741359</v>
       </c>
       <c r="G100" t="n">
         <v>43.05644186060967</v>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>-3.029772958994332</v>
+        <v>-9.029772958994339</v>
       </c>
       <c r="G101" t="n">
         <v>42.89176475443433</v>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>-2.73581077192851</v>
+        <v>-8.735810771928518</v>
       </c>
       <c r="G102" t="n">
         <v>42.91584098081738</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>-2.657381628969842</v>
+        <v>-8.657381628969851</v>
       </c>
       <c r="G103" t="n">
         <v>42.74162276938289</v>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>-2.985867677575239</v>
+        <v>-8.985867677575248</v>
       </c>
       <c r="G104" t="n">
         <v>42.72640173899076</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>-2.211212977030921</v>
+        <v>-8.211212977030929</v>
       </c>
       <c r="G105" t="n">
         <v>43.32495874830874</v>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>-2.320901966195391</v>
+        <v>-8.320901966195398</v>
       </c>
       <c r="G106" t="n">
         <v>43.46831076142712</v>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>-1.860044584584739</v>
+        <v>-7.860044584584748</v>
       </c>
       <c r="G107" t="n">
         <v>43.43965795680131</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>-2.970779891400893</v>
+        <v>-8.970779891400902</v>
       </c>
       <c r="G108" t="n">
         <v>42.57583356681521</v>
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>-3.170155862037196</v>
+        <v>-9.170155862037205</v>
       </c>
       <c r="G109" t="n">
         <v>42.94717734094524</v>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>-2.363095484119638</v>
+        <v>-8.363095484119645</v>
       </c>
       <c r="G110" t="n">
         <v>43.22533276302141</v>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>-2.207874117552794</v>
+        <v>-8.207874117552803</v>
       </c>
       <c r="G111" t="n">
         <v>43.54066208582352</v>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>-2.737909566831735</v>
+        <v>-8.737909566831743</v>
       </c>
       <c r="G112" t="n">
         <v>42.78760107797914</v>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>-2.308208095349812</v>
+        <v>-8.308208095349821</v>
       </c>
       <c r="G113" t="n">
         <v>43.3508622357155</v>
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>-2.500746070610181</v>
+        <v>-8.500746070610189</v>
       </c>
       <c r="G114" t="n">
         <v>43.32840797233777</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>-2.531852548056411</v>
+        <v>-8.53185254805642</v>
       </c>
       <c r="G115" t="n">
         <v>42.89154990928035</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>-2.023788849789965</v>
+        <v>-8.023788849789973</v>
       </c>
       <c r="G116" t="n">
         <v>43.15137999933746</v>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>-2.444996988511889</v>
+        <v>-8.444996988511898</v>
       </c>
       <c r="G117" t="n">
         <v>42.98150156229158</v>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>-2.348295207878113</v>
+        <v>-8.348295207878122</v>
       </c>
       <c r="G118" t="n">
         <v>43.30956877881584</v>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>-2.226178198668359</v>
+        <v>-8.226178198668368</v>
       </c>
       <c r="G119" t="n">
         <v>43.49438864972537</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>-2.578347989771348</v>
+        <v>-8.578347989771357</v>
       </c>
       <c r="G120" t="n">
         <v>42.85479997194844</v>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>-1.922733702777709</v>
+        <v>-7.922733702777719</v>
       </c>
       <c r="G121" t="n">
         <v>43.53834885451514</v>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>-2.435138506387183</v>
+        <v>-8.43513850638719</v>
       </c>
       <c r="G122" t="n">
         <v>43.36966761030885</v>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>-2.845379957598933</v>
+        <v>-8.845379957598942</v>
       </c>
       <c r="G123" t="n">
         <v>42.8325263722349</v>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>-2.165856916196512</v>
+        <v>-8.165856916196521</v>
       </c>
       <c r="G124" t="n">
         <v>43.43965054963625</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>-3.0483566689213</v>
+        <v>-9.048356668921308</v>
       </c>
       <c r="G125" t="n">
         <v>43.1011629158779</v>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>-2.157289215320035</v>
+        <v>-8.157289215320043</v>
       </c>
       <c r="G239" t="n">
         <v>42.39795346412646</v>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>-1.794417155665992</v>
+        <v>-7.794417155666</v>
       </c>
       <c r="G240" t="n">
         <v>42.18278182147874</v>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>-1.867053601225507</v>
+        <v>-7.867053601225515</v>
       </c>
       <c r="G241" t="n">
         <v>42.33619342330225</v>
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>-1.005505072871706</v>
+        <v>-7.005505072871713</v>
       </c>
       <c r="G242" t="n">
         <v>42.4183605612434</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>-2.113717122508475</v>
+        <v>-8.113717122508485</v>
       </c>
       <c r="G243" t="n">
         <v>42.2916510045028</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>-2.055292777148656</v>
+        <v>-8.055292777148665</v>
       </c>
       <c r="G244" t="n">
         <v>41.94101731784708</v>
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>-1.943185215918123</v>
+        <v>-7.943185215918132</v>
       </c>
       <c r="G245" t="n">
         <v>42.14602636633268</v>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>-2.056415280275513</v>
+        <v>-8.056415280275521</v>
       </c>
       <c r="G246" t="n">
         <v>42.43603699374314</v>
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>-0.8625839321231518</v>
+        <v>-6.86258393212316</v>
       </c>
       <c r="G247" t="n">
         <v>42.38874939169047</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>-2.193118804283134</v>
+        <v>-8.193118804283142</v>
       </c>
       <c r="G248" t="n">
         <v>42.15384748519664</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>-1.64129534107808</v>
+        <v>-7.641295341078088</v>
       </c>
       <c r="G249" t="n">
         <v>41.95276958920449</v>
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>-1.509272741489286</v>
+        <v>-7.509272741489295</v>
       </c>
       <c r="G250" t="n">
         <v>42.38489163653953</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>-1.125485076625873</v>
+        <v>-7.125485076625882</v>
       </c>
       <c r="G251" t="n">
         <v>42.39444092331676</v>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>-1.950032962178306</v>
+        <v>-7.950032962178315</v>
       </c>
       <c r="G252" t="n">
         <v>42.35590492463772</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>-1.818887721131923</v>
+        <v>-7.818887721131932</v>
       </c>
       <c r="G253" t="n">
         <v>42.2901190137455</v>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>-1.981151524649366</v>
+        <v>-7.981151524649375</v>
       </c>
       <c r="G254" t="n">
         <v>41.95614484521879</v>
@@ -9095,7 +9095,7 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>-1.678998547486863</v>
+        <v>-7.678998547486872</v>
       </c>
       <c r="G255" t="n">
         <v>42.12547419173919</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>-1.465028707809272</v>
+        <v>-7.46502870780928</v>
       </c>
       <c r="G256" t="n">
         <v>41.93229190861292</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>-1.84877813386191</v>
+        <v>-7.848778133861919</v>
       </c>
       <c r="G257" t="n">
         <v>42.3578598080344</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>-1.706392761275467</v>
+        <v>-7.706392761275476</v>
       </c>
       <c r="G258" t="n">
         <v>42.0586444925318</v>
